--- a/s60_signal/position-6881-6886-800.xlsx
+++ b/s60_signal/position-6881-6886-800.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6136" uniqueCount="814">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6166" uniqueCount="817">
   <si>
     <t>trade_time</t>
   </si>
@@ -1117,25 +1117,25 @@
     <t>2021-07-26</t>
   </si>
   <si>
-    <t>2021-06-04</t>
+    <t>2021-07-19</t>
   </si>
   <si>
-    <t>2021-06-09</t>
+    <t>2021-06-03</t>
   </si>
   <si>
     <t>2021-07-14</t>
   </si>
   <si>
-    <t>2021-07-19</t>
-  </si>
-  <si>
     <t>2021-07-27</t>
   </si>
   <si>
-    <t>2021-06-03</t>
+    <t>2021-07-15</t>
   </si>
   <si>
-    <t>2021-06-15</t>
+    <t>2021-07-20</t>
+  </si>
+  <si>
+    <t>2021-06-11</t>
   </si>
   <si>
     <t>2021-07-06</t>
@@ -1144,10 +1144,7 @@
     <t>2021-07-28</t>
   </si>
   <si>
-    <t>2021-07-15</t>
-  </si>
-  <si>
-    <t>2021-07-20</t>
+    <t>2021-08-02</t>
   </si>
   <si>
     <t>2021-06-17</t>
@@ -1169,6 +1166,9 @@
   </si>
   <si>
     <t>2021-07-30</t>
+  </si>
+  <si>
+    <t>2021-08-03</t>
   </si>
   <si>
     <t>2016-01-06</t>
@@ -2443,19 +2443,28 @@
     <t>2021-06-02</t>
   </si>
   <si>
+    <t>2021-06-04</t>
+  </si>
+  <si>
     <t>2021-06-08</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
   </si>
   <si>
     <t>2021-06-10</t>
   </si>
   <si>
-    <t>2021-06-11</t>
+    <t>2021-06-15</t>
   </si>
   <si>
     <t>2021-06-18</t>
   </si>
   <si>
     <t>2021-06-28</t>
+  </si>
+  <si>
+    <t>2021-07-29</t>
   </si>
 </sst>
 </file>
@@ -2813,7 +2822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P2061"/>
+  <dimension ref="A1:P2070"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -96690,7 +96699,7 @@
         <v>5.218027229384798</v>
       </c>
       <c r="D1901" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="E1901">
         <v>4.925638640730162</v>
@@ -97090,7 +97099,7 @@
         <v>4.781161008967361</v>
       </c>
       <c r="D1909" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="E1909">
         <v>4.50214587603979</v>
@@ -97590,7 +97599,7 @@
         <v>4.303088561031202</v>
       </c>
       <c r="D1919" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="E1919">
         <v>4.038708298958818</v>
@@ -98119,7 +98128,7 @@
         <v>3.737983589108724</v>
       </c>
       <c r="D1930" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="E1930">
         <v>3.490902458829886</v>
@@ -98813,10 +98822,10 @@
         <v>0</v>
       </c>
       <c r="B1944" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="C1944">
-        <v>-2.50753631058668</v>
+        <v>-2.501593339837639</v>
       </c>
       <c r="D1944" t="s">
         <v>623</v>
@@ -98828,22 +98837,22 @@
         <v>1</v>
       </c>
       <c r="G1944">
-        <v>0.02446753631058668</v>
+        <v>0.02494159333983764</v>
       </c>
       <c r="H1944">
         <v>0.02410719363805387</v>
       </c>
       <c r="I1944">
-        <v>0.4003426725328119</v>
+        <v>0.3943997017837706</v>
       </c>
       <c r="J1944">
         <v>2.925712865637024</v>
       </c>
       <c r="K1944">
-        <v>4.61</v>
+        <v>4.69</v>
       </c>
       <c r="L1944">
-        <v>10.98</v>
+        <v>11.22</v>
       </c>
       <c r="M1944">
         <v>4.48</v>
@@ -98863,10 +98872,10 @@
         <v>1</v>
       </c>
       <c r="B1945" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C1945">
-        <v>-2.643079082524901</v>
+        <v>-2.50753631058668</v>
       </c>
       <c r="D1945" t="s">
         <v>623</v>
@@ -98878,22 +98887,22 @@
         <v>1</v>
       </c>
       <c r="G1945">
-        <v>0.0246830790825249</v>
+        <v>0.02446753631058668</v>
       </c>
       <c r="H1945">
         <v>0.02410719363805387</v>
       </c>
       <c r="I1945">
-        <v>0.5358854444710328</v>
+        <v>0.4003426725328119</v>
       </c>
       <c r="J1945">
         <v>2.925712865637024</v>
       </c>
       <c r="K1945">
-        <v>4.67</v>
+        <v>4.61</v>
       </c>
       <c r="L1945">
-        <v>11.02</v>
+        <v>10.98</v>
       </c>
       <c r="M1945">
         <v>4.48</v>
@@ -98913,43 +98922,43 @@
         <v>2</v>
       </c>
       <c r="B1946" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="C1946">
-        <v>-2.683421755057713</v>
+        <v>-2.643079082524901</v>
       </c>
       <c r="D1946" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E1946">
-        <v>-2.041250667304828</v>
+        <v>-2.107193638053868</v>
       </c>
       <c r="F1946">
         <v>1</v>
       </c>
       <c r="G1946">
-        <v>0.02540342175505771</v>
+        <v>0.0246830790825249</v>
       </c>
       <c r="H1946">
-        <v>0.02464125066730483</v>
+        <v>0.02410719363805387</v>
       </c>
       <c r="I1946">
-        <v>0.6421710877528852</v>
+        <v>0.5358854444710328</v>
       </c>
       <c r="J1946">
         <v>2.925712865637024</v>
       </c>
       <c r="K1946">
-        <v>4.8</v>
+        <v>4.67</v>
       </c>
       <c r="L1946">
-        <v>11.36</v>
+        <v>11.02</v>
       </c>
       <c r="M1946">
-        <v>4.56</v>
+        <v>4.48</v>
       </c>
       <c r="N1946">
-        <v>11.3</v>
+        <v>11</v>
       </c>
       <c r="O1946">
         <v>1</v>
@@ -98963,10 +98972,10 @@
         <v>3</v>
       </c>
       <c r="B1947" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C1947">
-        <v>-2.515650369088602</v>
+        <v>-2.683421755057713</v>
       </c>
       <c r="D1947" t="s">
         <v>624</v>
@@ -98978,22 +98987,22 @@
         <v>1</v>
       </c>
       <c r="G1947">
-        <v>0.0253956503690886</v>
+        <v>0.02540342175505771</v>
       </c>
       <c r="H1947">
         <v>0.02464125066730483</v>
       </c>
       <c r="I1947">
-        <v>0.4743997017837742</v>
+        <v>0.6421710877528852</v>
       </c>
       <c r="J1947">
         <v>2.925712865637024</v>
       </c>
       <c r="K1947">
-        <v>4.77</v>
+        <v>4.8</v>
       </c>
       <c r="L1947">
-        <v>11.44</v>
+        <v>11.36</v>
       </c>
       <c r="M1947">
         <v>4.56</v>
@@ -99013,46 +99022,46 @@
         <v>4</v>
       </c>
       <c r="B1948" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C1948">
-        <v>-1.679079579551942</v>
+        <v>-2.515650369088602</v>
       </c>
       <c r="D1948" t="s">
-        <v>384</v>
+        <v>624</v>
       </c>
       <c r="E1948">
-        <v>-1.578394234486314</v>
+        <v>-2.041250667304828</v>
       </c>
       <c r="F1948">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1948">
-        <v>0.02359907957955194</v>
+        <v>0.0253956503690886</v>
       </c>
       <c r="H1948">
-        <v>0.02217839423448632</v>
+        <v>0.02464125066730483</v>
       </c>
       <c r="I1948">
-        <v>-0.100685345065628</v>
+        <v>0.4743997017837742</v>
       </c>
       <c r="J1948">
         <v>2.925712865637024</v>
       </c>
       <c r="K1948">
-        <v>4.32</v>
+        <v>4.77</v>
       </c>
       <c r="L1948">
-        <v>10.96</v>
+        <v>11.44</v>
       </c>
       <c r="M1948">
-        <v>4.06</v>
+        <v>4.56</v>
       </c>
       <c r="N1948">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="O1948">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1948" t="s">
         <v>802</v>
@@ -99060,146 +99069,146 @@
     </row>
     <row r="1949" spans="1:16">
       <c r="A1949" s="1">
+        <v>5</v>
+      </c>
+      <c r="B1949" t="s">
+        <v>365</v>
+      </c>
+      <c r="C1949">
+        <v>-1.679079579551942</v>
+      </c>
+      <c r="D1949" t="s">
+        <v>384</v>
+      </c>
+      <c r="E1949">
+        <v>-1.615765421644612</v>
+      </c>
+      <c r="F1949">
+        <v>-1</v>
+      </c>
+      <c r="G1949">
+        <v>0.02359907957955194</v>
+      </c>
+      <c r="H1949">
+        <v>0.02313576542164461</v>
+      </c>
+      <c r="I1949">
+        <v>-0.06331415790732997</v>
+      </c>
+      <c r="J1949">
+        <v>2.925712865637024</v>
+      </c>
+      <c r="K1949">
+        <v>4.32</v>
+      </c>
+      <c r="L1949">
+        <v>10.96</v>
+      </c>
+      <c r="M1949">
+        <v>4.23</v>
+      </c>
+      <c r="N1949">
+        <v>10.76</v>
+      </c>
+      <c r="O1949">
         <v>0</v>
       </c>
-      <c r="B1949" t="s">
-        <v>363</v>
-      </c>
-      <c r="C1949">
-        <v>-3.012111487684564</v>
-      </c>
-      <c r="D1949" t="s">
-        <v>623</v>
-      </c>
-      <c r="E1949">
-        <v>-2.461211876836584</v>
-      </c>
-      <c r="F1949">
-        <v>1</v>
-      </c>
-      <c r="G1949">
-        <v>0.02505211148768456</v>
-      </c>
-      <c r="H1949">
-        <v>0.02446121187683659</v>
-      </c>
-      <c r="I1949">
-        <v>0.5508996108479796</v>
-      </c>
-      <c r="J1949">
-        <v>3.004734793936737</v>
-      </c>
-      <c r="K1949">
-        <v>4.67</v>
-      </c>
-      <c r="L1949">
-        <v>11.02</v>
-      </c>
-      <c r="M1949">
-        <v>4.48</v>
-      </c>
-      <c r="N1949">
-        <v>11</v>
-      </c>
-      <c r="O1949">
-        <v>1</v>
-      </c>
       <c r="P1949" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="1950" spans="1:16">
       <c r="A1950" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B1950" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="C1950">
-        <v>-3.062727010896339</v>
+        <v>-1.68947977836276</v>
       </c>
       <c r="D1950" t="s">
-        <v>624</v>
+        <v>384</v>
       </c>
       <c r="E1950">
-        <v>-2.401590660351523</v>
+        <v>-1.615765421644612</v>
       </c>
       <c r="F1950">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1950">
-        <v>0.02578272701089634</v>
+        <v>0.02276947977836276</v>
       </c>
       <c r="H1950">
-        <v>0.02500159066035152</v>
+        <v>0.02313576542164461</v>
       </c>
       <c r="I1950">
-        <v>0.6611363505448153</v>
+        <v>-0.0737143567181473</v>
       </c>
       <c r="J1950">
-        <v>3.004734793936737</v>
+        <v>2.925712865637024</v>
       </c>
       <c r="K1950">
-        <v>4.8</v>
+        <v>4.18</v>
       </c>
       <c r="L1950">
-        <v>11.36</v>
+        <v>10.54</v>
       </c>
       <c r="M1950">
-        <v>4.56</v>
+        <v>4.23</v>
       </c>
       <c r="N1950">
-        <v>11.3</v>
+        <v>10.76</v>
       </c>
       <c r="O1950">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1950" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="1951" spans="1:16">
       <c r="A1951" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B1951" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="C1951">
-        <v>-2.892584967078236</v>
+        <v>-2.872206183563296</v>
       </c>
       <c r="D1951" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E1951">
-        <v>-2.401590660351523</v>
+        <v>-2.461211876836584</v>
       </c>
       <c r="F1951">
         <v>1</v>
       </c>
       <c r="G1951">
-        <v>0.02577258496707823</v>
+        <v>0.0253122061835633</v>
       </c>
       <c r="H1951">
-        <v>0.02500159066035152</v>
+        <v>0.02446121187683659</v>
       </c>
       <c r="I1951">
-        <v>0.4909943067267122</v>
+        <v>0.4109943067267121</v>
       </c>
       <c r="J1951">
         <v>3.004734793936737</v>
       </c>
       <c r="K1951">
-        <v>4.77</v>
+        <v>4.69</v>
       </c>
       <c r="L1951">
-        <v>11.44</v>
+        <v>11.22</v>
       </c>
       <c r="M1951">
-        <v>4.56</v>
+        <v>4.48</v>
       </c>
       <c r="N1951">
-        <v>11.3</v>
+        <v>11</v>
       </c>
       <c r="O1951">
         <v>1</v>
@@ -99210,49 +99219,49 @@
     </row>
     <row r="1952" spans="1:16">
       <c r="A1952" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1952" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C1952">
-        <v>-2.020454309806706</v>
+        <v>-2.871827400048359</v>
       </c>
       <c r="D1952" t="s">
-        <v>384</v>
+        <v>623</v>
       </c>
       <c r="E1952">
-        <v>-1.899223263383151</v>
+        <v>-2.461211876836584</v>
       </c>
       <c r="F1952">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1952">
-        <v>0.02394045430980671</v>
+        <v>0.02483182740004836</v>
       </c>
       <c r="H1952">
-        <v>0.02249922326338315</v>
+        <v>0.02446121187683659</v>
       </c>
       <c r="I1952">
-        <v>-0.1212310464235546</v>
+        <v>0.4106155232117743</v>
       </c>
       <c r="J1952">
         <v>3.004734793936737</v>
       </c>
       <c r="K1952">
-        <v>4.32</v>
+        <v>4.61</v>
       </c>
       <c r="L1952">
-        <v>10.96</v>
+        <v>10.98</v>
       </c>
       <c r="M1952">
-        <v>4.06</v>
+        <v>4.48</v>
       </c>
       <c r="N1952">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="O1952">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1952" t="s">
         <v>803</v>
@@ -99260,34 +99269,34 @@
     </row>
     <row r="1953" spans="1:16">
       <c r="A1953" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1953" t="s">
         <v>363</v>
       </c>
       <c r="C1953">
-        <v>-3.31690489875729</v>
+        <v>-3.012111487684564</v>
       </c>
       <c r="D1953" t="s">
         <v>623</v>
       </c>
       <c r="E1953">
-        <v>-2.753604699450248</v>
+        <v>-2.461211876836584</v>
       </c>
       <c r="F1953">
         <v>1</v>
       </c>
       <c r="G1953">
-        <v>0.02535690489875729</v>
+        <v>0.02505211148768456</v>
       </c>
       <c r="H1953">
-        <v>0.02475360469945025</v>
+        <v>0.02446121187683659</v>
       </c>
       <c r="I1953">
-        <v>0.5633001993070419</v>
+        <v>0.5508996108479796</v>
       </c>
       <c r="J1953">
-        <v>3.07000104898443</v>
+        <v>3.004734793936737</v>
       </c>
       <c r="K1953">
         <v>4.67</v>
@@ -99305,39 +99314,39 @@
         <v>1</v>
       </c>
       <c r="P1953" t="s">
-        <v>353</v>
+        <v>803</v>
       </c>
     </row>
     <row r="1954" spans="1:16">
       <c r="A1954" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1954" t="s">
         <v>356</v>
       </c>
       <c r="C1954">
-        <v>-3.376005035125266</v>
+        <v>-3.062727010896339</v>
       </c>
       <c r="D1954" t="s">
         <v>624</v>
       </c>
       <c r="E1954">
-        <v>-2.699204783369003</v>
+        <v>-2.401590660351523</v>
       </c>
       <c r="F1954">
         <v>1</v>
       </c>
       <c r="G1954">
-        <v>0.02609600503512527</v>
+        <v>0.02578272701089634</v>
       </c>
       <c r="H1954">
-        <v>0.02529920478336901</v>
+        <v>0.02500159066035152</v>
       </c>
       <c r="I1954">
-        <v>0.6768002517562621</v>
+        <v>0.6611363505448153</v>
       </c>
       <c r="J1954">
-        <v>3.07000104898443</v>
+        <v>3.004734793936737</v>
       </c>
       <c r="K1954">
         <v>4.8</v>
@@ -99355,39 +99364,39 @@
         <v>1</v>
       </c>
       <c r="P1954" t="s">
-        <v>353</v>
+        <v>803</v>
       </c>
     </row>
     <row r="1955" spans="1:16">
       <c r="A1955" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B1955" t="s">
         <v>364</v>
       </c>
       <c r="C1955">
-        <v>-3.203905003655732</v>
+        <v>-2.892584967078236</v>
       </c>
       <c r="D1955" t="s">
         <v>624</v>
       </c>
       <c r="E1955">
-        <v>-2.699204783369003</v>
+        <v>-2.401590660351523</v>
       </c>
       <c r="F1955">
         <v>1</v>
       </c>
       <c r="G1955">
-        <v>0.02608390500365573</v>
+        <v>0.02577258496707823</v>
       </c>
       <c r="H1955">
-        <v>0.02529920478336901</v>
+        <v>0.02500159066035152</v>
       </c>
       <c r="I1955">
-        <v>0.504700220286729</v>
+        <v>0.4909943067267122</v>
       </c>
       <c r="J1955">
-        <v>3.07000104898443</v>
+        <v>3.004734793936737</v>
       </c>
       <c r="K1955">
         <v>4.77</v>
@@ -99405,39 +99414,39 @@
         <v>1</v>
       </c>
       <c r="P1955" t="s">
-        <v>353</v>
+        <v>803</v>
       </c>
     </row>
     <row r="1956" spans="1:16">
       <c r="A1956" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B1956" t="s">
         <v>365</v>
       </c>
       <c r="C1956">
-        <v>-2.302404531612739</v>
+        <v>-2.020454309806706</v>
       </c>
       <c r="D1956" t="s">
         <v>384</v>
       </c>
       <c r="E1956">
-        <v>-2.164204258876785</v>
+        <v>-1.950028178352401</v>
       </c>
       <c r="F1956">
         <v>-1</v>
       </c>
       <c r="G1956">
-        <v>0.02422240453161274</v>
+        <v>0.02394045430980671</v>
       </c>
       <c r="H1956">
-        <v>0.02276420425887679</v>
+        <v>0.0234700281783524</v>
       </c>
       <c r="I1956">
-        <v>-0.1382002727359541</v>
+        <v>-0.07042613145430465</v>
       </c>
       <c r="J1956">
-        <v>3.07000104898443</v>
+        <v>3.004734793936737</v>
       </c>
       <c r="K1956">
         <v>4.32</v>
@@ -99446,48 +99455,48 @@
         <v>10.96</v>
       </c>
       <c r="M1956">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="N1956">
-        <v>10.3</v>
+        <v>10.76</v>
       </c>
       <c r="O1956">
         <v>0</v>
       </c>
       <c r="P1956" t="s">
-        <v>353</v>
+        <v>803</v>
       </c>
     </row>
     <row r="1957" spans="1:16">
       <c r="A1957" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B1957" t="s">
         <v>366</v>
       </c>
       <c r="C1957">
-        <v>-2.292604384754918</v>
+        <v>-2.019791438655561</v>
       </c>
       <c r="D1957" t="s">
         <v>384</v>
       </c>
       <c r="E1957">
-        <v>-2.164204258876785</v>
+        <v>-1.950028178352401</v>
       </c>
       <c r="F1957">
         <v>-1</v>
       </c>
       <c r="G1957">
-        <v>0.02337260438475492</v>
+        <v>0.02309979143865556</v>
       </c>
       <c r="H1957">
-        <v>0.02276420425887679</v>
+        <v>0.0234700281783524</v>
       </c>
       <c r="I1957">
-        <v>-0.1284001258781338</v>
+        <v>-0.06976326030316038</v>
       </c>
       <c r="J1957">
-        <v>3.07000104898443</v>
+        <v>3.004734793936737</v>
       </c>
       <c r="K1957">
         <v>4.18</v>
@@ -99496,16 +99505,16 @@
         <v>10.54</v>
       </c>
       <c r="M1957">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="N1957">
-        <v>10.3</v>
+        <v>10.76</v>
       </c>
       <c r="O1957">
         <v>0</v>
       </c>
       <c r="P1957" t="s">
-        <v>353</v>
+        <v>803</v>
       </c>
     </row>
     <row r="1958" spans="1:16">
@@ -99513,49 +99522,49 @@
         <v>0</v>
       </c>
       <c r="B1958" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C1958">
-        <v>-3.31746358241166</v>
+        <v>-3.31690489875729</v>
       </c>
       <c r="D1958" t="s">
-        <v>361</v>
+        <v>623</v>
       </c>
       <c r="E1958">
-        <v>-2.806092527650396</v>
+        <v>-2.753604699450248</v>
       </c>
       <c r="F1958">
         <v>1</v>
       </c>
       <c r="G1958">
-        <v>0.02639746358241166</v>
+        <v>0.02535690489875729</v>
       </c>
       <c r="H1958">
-        <v>0.0256060925276504</v>
+        <v>0.02475360469945025</v>
       </c>
       <c r="I1958">
-        <v>0.5113710547612644</v>
+        <v>0.5633001993070419</v>
       </c>
       <c r="J1958">
-        <v>3.101766927434584</v>
+        <v>3.07000104898443</v>
       </c>
       <c r="K1958">
-        <v>4.79</v>
+        <v>4.67</v>
       </c>
       <c r="L1958">
-        <v>11.54</v>
+        <v>11.02</v>
       </c>
       <c r="M1958">
-        <v>4.58</v>
+        <v>4.48</v>
       </c>
       <c r="N1958">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="O1958">
         <v>1</v>
       </c>
       <c r="P1958" t="s">
-        <v>804</v>
+        <v>353</v>
       </c>
     </row>
     <row r="1959" spans="1:16">
@@ -99563,49 +99572,49 @@
         <v>1</v>
       </c>
       <c r="B1959" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="C1959">
-        <v>-3.240339897491237</v>
+        <v>-3.376005035125266</v>
       </c>
       <c r="D1959" t="s">
-        <v>361</v>
+        <v>624</v>
       </c>
       <c r="E1959">
-        <v>-2.806092527650396</v>
+        <v>-2.699204783369003</v>
       </c>
       <c r="F1959">
         <v>1</v>
       </c>
       <c r="G1959">
-        <v>0.02604033989749124</v>
+        <v>0.02609600503512527</v>
       </c>
       <c r="H1959">
-        <v>0.0256060925276504</v>
+        <v>0.02529920478336901</v>
       </c>
       <c r="I1959">
-        <v>0.4342473698408416</v>
+        <v>0.6768002517562621</v>
       </c>
       <c r="J1959">
-        <v>3.101766927434584</v>
+        <v>3.07000104898443</v>
       </c>
       <c r="K1959">
-        <v>4.72</v>
+        <v>4.8</v>
       </c>
       <c r="L1959">
-        <v>11.4</v>
+        <v>11.36</v>
       </c>
       <c r="M1959">
-        <v>4.58</v>
+        <v>4.56</v>
       </c>
       <c r="N1959">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="O1959">
         <v>1</v>
       </c>
       <c r="P1959" t="s">
-        <v>804</v>
+        <v>353</v>
       </c>
     </row>
     <row r="1960" spans="1:16">
@@ -99613,49 +99622,49 @@
         <v>2</v>
       </c>
       <c r="B1960" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C1960">
-        <v>-2.382509441596982</v>
+        <v>-3.203905003655732</v>
       </c>
       <c r="D1960" t="s">
-        <v>384</v>
+        <v>624</v>
       </c>
       <c r="E1960">
-        <v>-2.29317372538441</v>
+        <v>-2.699204783369003</v>
       </c>
       <c r="F1960">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1960">
-        <v>0.02398250944159698</v>
+        <v>0.02608390500365573</v>
       </c>
       <c r="H1960">
-        <v>0.02289317372538441</v>
+        <v>0.02529920478336901</v>
       </c>
       <c r="I1960">
-        <v>-0.08933571621257208</v>
+        <v>0.504700220286729</v>
       </c>
       <c r="J1960">
-        <v>3.101766927434584</v>
+        <v>3.07000104898443</v>
       </c>
       <c r="K1960">
-        <v>4.25</v>
+        <v>4.77</v>
       </c>
       <c r="L1960">
-        <v>10.8</v>
+        <v>11.44</v>
       </c>
       <c r="M1960">
-        <v>4.06</v>
+        <v>4.56</v>
       </c>
       <c r="N1960">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="O1960">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1960" t="s">
-        <v>804</v>
+        <v>353</v>
       </c>
     </row>
     <row r="1961" spans="1:16">
@@ -99663,49 +99672,49 @@
         <v>3</v>
       </c>
       <c r="B1961" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C1961">
-        <v>-2.373527110871329</v>
+        <v>-2.302404531612739</v>
       </c>
       <c r="D1961" t="s">
         <v>384</v>
       </c>
       <c r="E1961">
-        <v>-2.29317372538441</v>
+        <v>-2.226104437204141</v>
       </c>
       <c r="F1961">
         <v>-1</v>
       </c>
       <c r="G1961">
-        <v>0.02405352711087133</v>
+        <v>0.02422240453161274</v>
       </c>
       <c r="H1961">
-        <v>0.02289317372538441</v>
+        <v>0.02374610443720414</v>
       </c>
       <c r="I1961">
-        <v>-0.08035338548691939</v>
+        <v>-0.07630009440859808</v>
       </c>
       <c r="J1961">
-        <v>3.101766927434584</v>
+        <v>3.07000104898443</v>
       </c>
       <c r="K1961">
-        <v>4.26</v>
+        <v>4.32</v>
       </c>
       <c r="L1961">
-        <v>10.84</v>
+        <v>10.96</v>
       </c>
       <c r="M1961">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="N1961">
-        <v>10.3</v>
+        <v>10.76</v>
       </c>
       <c r="O1961">
         <v>0</v>
       </c>
       <c r="P1961" t="s">
-        <v>804</v>
+        <v>353</v>
       </c>
     </row>
     <row r="1962" spans="1:16">
@@ -99713,740 +99722,740 @@
         <v>4</v>
       </c>
       <c r="B1962" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C1962">
-        <v>-2.331138386835722</v>
+        <v>-2.238204468673672</v>
       </c>
       <c r="D1962" t="s">
         <v>384</v>
       </c>
       <c r="E1962">
-        <v>-2.29317372538441</v>
+        <v>-2.226104437204141</v>
       </c>
       <c r="F1962">
         <v>-1</v>
       </c>
       <c r="G1962">
-        <v>0.02273113838683572</v>
+        <v>0.02391820446867367</v>
       </c>
       <c r="H1962">
-        <v>0.02289317372538441</v>
+        <v>0.02374610443720414</v>
       </c>
       <c r="I1962">
-        <v>-0.03796466145131205</v>
+        <v>-0.0121000314695312</v>
       </c>
       <c r="J1962">
-        <v>3.101766927434584</v>
+        <v>3.07000104898443</v>
       </c>
       <c r="K1962">
-        <v>4.04</v>
+        <v>4.26</v>
       </c>
       <c r="L1962">
-        <v>10.2</v>
+        <v>10.84</v>
       </c>
       <c r="M1962">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="N1962">
-        <v>10.3</v>
+        <v>10.76</v>
       </c>
       <c r="O1962">
         <v>0</v>
       </c>
       <c r="P1962" t="s">
-        <v>804</v>
+        <v>353</v>
       </c>
     </row>
     <row r="1963" spans="1:16">
       <c r="A1963" s="1">
+        <v>5</v>
+      </c>
+      <c r="B1963" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1963">
+        <v>-2.292604384754918</v>
+      </c>
+      <c r="D1963" t="s">
+        <v>384</v>
+      </c>
+      <c r="E1963">
+        <v>-2.226104437204141</v>
+      </c>
+      <c r="F1963">
+        <v>-1</v>
+      </c>
+      <c r="G1963">
+        <v>0.02337260438475492</v>
+      </c>
+      <c r="H1963">
+        <v>0.02374610443720414</v>
+      </c>
+      <c r="I1963">
+        <v>-0.0664999475507777</v>
+      </c>
+      <c r="J1963">
+        <v>3.07000104898443</v>
+      </c>
+      <c r="K1963">
+        <v>4.18</v>
+      </c>
+      <c r="L1963">
+        <v>10.54</v>
+      </c>
+      <c r="M1963">
+        <v>4.23</v>
+      </c>
+      <c r="N1963">
+        <v>10.76</v>
+      </c>
+      <c r="O1963">
         <v>0</v>
       </c>
-      <c r="B1963" t="s">
-        <v>372</v>
-      </c>
-      <c r="C1963">
-        <v>-3.096478438550935</v>
-      </c>
-      <c r="D1963" t="s">
-        <v>361</v>
-      </c>
-      <c r="E1963">
-        <v>-2.674078157592271</v>
-      </c>
-      <c r="F1963">
-        <v>1</v>
-      </c>
-      <c r="G1963">
-        <v>0.02609647843855093</v>
-      </c>
-      <c r="H1963">
-        <v>0.02547407815759227</v>
-      </c>
-      <c r="I1963">
-        <v>0.422400280958664</v>
-      </c>
-      <c r="J1963">
-        <v>3.072942829168618</v>
-      </c>
-      <c r="K1963">
-        <v>4.75</v>
-      </c>
-      <c r="L1963">
-        <v>11.5</v>
-      </c>
-      <c r="M1963">
-        <v>4.58</v>
-      </c>
-      <c r="N1963">
-        <v>11.4</v>
-      </c>
-      <c r="O1963">
-        <v>1</v>
-      </c>
       <c r="P1963" t="s">
-        <v>805</v>
+        <v>353</v>
       </c>
     </row>
     <row r="1964" spans="1:16">
       <c r="A1964" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1964" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C1964">
-        <v>-2.260007023966626</v>
+        <v>-3.233392905314275</v>
       </c>
       <c r="D1964" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="E1964">
-        <v>-2.176147886424587</v>
+        <v>-2.744057189101705</v>
       </c>
       <c r="F1964">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1964">
-        <v>0.02386000702396663</v>
+        <v>0.02623339290531428</v>
       </c>
       <c r="H1964">
-        <v>0.02277614788642459</v>
+        <v>0.02554405718910171</v>
       </c>
       <c r="I1964">
-        <v>-0.08385913754203855</v>
+        <v>0.4893357162125707</v>
       </c>
       <c r="J1964">
-        <v>3.072942829168618</v>
+        <v>3.101766927434584</v>
       </c>
       <c r="K1964">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="L1964">
-        <v>10.8</v>
+        <v>11.5</v>
       </c>
       <c r="M1964">
-        <v>4.06</v>
+        <v>4.56</v>
       </c>
       <c r="N1964">
-        <v>10.3</v>
+        <v>11.4</v>
       </c>
       <c r="O1964">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1964" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="1965" spans="1:16">
       <c r="A1965" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1965" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C1965">
-        <v>-2.250736452258312</v>
+        <v>-2.382509441596982</v>
       </c>
       <c r="D1965" t="s">
         <v>384</v>
       </c>
       <c r="E1965">
-        <v>-2.176147886424587</v>
+        <v>-2.360474103048293</v>
       </c>
       <c r="F1965">
         <v>-1</v>
       </c>
       <c r="G1965">
-        <v>0.02393073645225831</v>
+        <v>0.02398250944159698</v>
       </c>
       <c r="H1965">
-        <v>0.02277614788642459</v>
+        <v>0.02388047410304829</v>
       </c>
       <c r="I1965">
-        <v>-0.07458856583372508</v>
+        <v>-0.02203533854868844</v>
       </c>
       <c r="J1965">
-        <v>3.072942829168618</v>
+        <v>3.101766927434584</v>
       </c>
       <c r="K1965">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="L1965">
-        <v>10.84</v>
+        <v>10.8</v>
       </c>
       <c r="M1965">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="N1965">
-        <v>10.3</v>
+        <v>10.76</v>
       </c>
       <c r="O1965">
         <v>0</v>
       </c>
       <c r="P1965" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="1966" spans="1:16">
       <c r="A1966" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1966" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C1966">
-        <v>-2.214689029841217</v>
+        <v>-2.373527110871329</v>
       </c>
       <c r="D1966" t="s">
         <v>384</v>
       </c>
       <c r="E1966">
-        <v>-2.176147886424587</v>
+        <v>-2.360474103048293</v>
       </c>
       <c r="F1966">
         <v>-1</v>
       </c>
       <c r="G1966">
-        <v>0.02261468902984122</v>
+        <v>0.02405352711087133</v>
       </c>
       <c r="H1966">
-        <v>0.02277614788642459</v>
+        <v>0.02388047410304829</v>
       </c>
       <c r="I1966">
-        <v>-0.03854114341663006</v>
+        <v>-0.01305300782303576</v>
       </c>
       <c r="J1966">
-        <v>3.072942829168618</v>
+        <v>3.101766927434584</v>
       </c>
       <c r="K1966">
-        <v>4.04</v>
+        <v>4.26</v>
       </c>
       <c r="L1966">
-        <v>10.2</v>
+        <v>10.84</v>
       </c>
       <c r="M1966">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="N1966">
-        <v>10.3</v>
+        <v>10.76</v>
       </c>
       <c r="O1966">
         <v>0</v>
       </c>
       <c r="P1966" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="1967" spans="1:16">
       <c r="A1967" s="1">
+        <v>3</v>
+      </c>
+      <c r="B1967" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1967">
+        <v>-2.331138386835722</v>
+      </c>
+      <c r="D1967" t="s">
+        <v>384</v>
+      </c>
+      <c r="E1967">
+        <v>-2.360474103048293</v>
+      </c>
+      <c r="F1967">
+        <v>-1</v>
+      </c>
+      <c r="G1967">
+        <v>0.02273113838683572</v>
+      </c>
+      <c r="H1967">
+        <v>0.02388047410304829</v>
+      </c>
+      <c r="I1967">
+        <v>0.02933571621257158</v>
+      </c>
+      <c r="J1967">
+        <v>3.101766927434584</v>
+      </c>
+      <c r="K1967">
+        <v>4.04</v>
+      </c>
+      <c r="L1967">
+        <v>10.2</v>
+      </c>
+      <c r="M1967">
+        <v>4.23</v>
+      </c>
+      <c r="N1967">
+        <v>10.76</v>
+      </c>
+      <c r="O1967">
         <v>0</v>
       </c>
-      <c r="B1967" t="s">
-        <v>372</v>
-      </c>
-      <c r="C1967">
-        <v>-3.040827059344563</v>
-      </c>
-      <c r="D1967" t="s">
-        <v>360</v>
-      </c>
-      <c r="E1967">
-        <v>-2.559193976970782</v>
-      </c>
-      <c r="F1967">
-        <v>1</v>
-      </c>
-      <c r="G1967">
-        <v>0.02604082705934457</v>
-      </c>
-      <c r="H1967">
-        <v>0.02535919397697078</v>
-      </c>
-      <c r="I1967">
-        <v>0.4816330823737811</v>
-      </c>
-      <c r="J1967">
-        <v>3.061226749335697</v>
-      </c>
-      <c r="K1967">
-        <v>4.75</v>
-      </c>
-      <c r="L1967">
-        <v>11.5</v>
-      </c>
-      <c r="M1967">
-        <v>4.56</v>
-      </c>
-      <c r="N1967">
-        <v>11.4</v>
-      </c>
-      <c r="O1967">
-        <v>1</v>
-      </c>
       <c r="P1967" t="s">
-        <v>356</v>
+        <v>804</v>
       </c>
     </row>
     <row r="1968" spans="1:16">
       <c r="A1968" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1968" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C1968">
-        <v>-2.210213684676713</v>
+        <v>-3.096478438550935</v>
       </c>
       <c r="D1968" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="E1968">
-        <v>-2.128580602302931</v>
+        <v>-2.6126193010089</v>
       </c>
       <c r="F1968">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1968">
-        <v>0.02381021368467671</v>
+        <v>0.02609647843855093</v>
       </c>
       <c r="H1968">
-        <v>0.02272858060230293</v>
+        <v>0.0254126193010089</v>
       </c>
       <c r="I1968">
-        <v>-0.08163308237378253</v>
+        <v>0.4838591375420354</v>
       </c>
       <c r="J1968">
-        <v>3.061226749335697</v>
+        <v>3.072942829168618</v>
       </c>
       <c r="K1968">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="L1968">
-        <v>10.8</v>
+        <v>11.5</v>
       </c>
       <c r="M1968">
-        <v>4.06</v>
+        <v>4.56</v>
       </c>
       <c r="N1968">
-        <v>10.3</v>
+        <v>11.4</v>
       </c>
       <c r="O1968">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1968" t="s">
-        <v>356</v>
+        <v>805</v>
       </c>
     </row>
     <row r="1969" spans="1:16">
       <c r="A1969" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1969" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C1969">
-        <v>-2.200825952170071</v>
+        <v>-2.210736452258312</v>
       </c>
       <c r="D1969" t="s">
         <v>384</v>
       </c>
       <c r="E1969">
-        <v>-2.128580602302931</v>
+        <v>-2.238548167383255</v>
       </c>
       <c r="F1969">
         <v>-1</v>
       </c>
       <c r="G1969">
-        <v>0.02388082595217007</v>
+        <v>0.02397073645225832</v>
       </c>
       <c r="H1969">
-        <v>0.02272858060230293</v>
+        <v>0.02375854816738325</v>
       </c>
       <c r="I1969">
-        <v>-0.07224534986714026</v>
+        <v>0.02781171512494396</v>
       </c>
       <c r="J1969">
-        <v>3.061226749335697</v>
+        <v>3.072942829168618</v>
       </c>
       <c r="K1969">
         <v>4.26</v>
       </c>
       <c r="L1969">
-        <v>10.84</v>
+        <v>10.88</v>
       </c>
       <c r="M1969">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="N1969">
-        <v>10.3</v>
+        <v>10.76</v>
       </c>
       <c r="O1969">
         <v>0</v>
       </c>
       <c r="P1969" t="s">
-        <v>356</v>
+        <v>805</v>
       </c>
     </row>
     <row r="1970" spans="1:16">
       <c r="A1970" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1970" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C1970">
-        <v>-2.167356067316218</v>
+        <v>-2.250736452258312</v>
       </c>
       <c r="D1970" t="s">
         <v>384</v>
       </c>
       <c r="E1970">
-        <v>-2.128580602302931</v>
+        <v>-2.238548167383255</v>
       </c>
       <c r="F1970">
         <v>-1</v>
       </c>
       <c r="G1970">
-        <v>0.02256735606731622</v>
+        <v>0.02393073645225831</v>
       </c>
       <c r="H1970">
-        <v>0.02272858060230293</v>
+        <v>0.02375854816738325</v>
       </c>
       <c r="I1970">
-        <v>-0.03877546501328766</v>
+        <v>-0.01218828487505697</v>
       </c>
       <c r="J1970">
-        <v>3.061226749335697</v>
+        <v>3.072942829168618</v>
       </c>
       <c r="K1970">
-        <v>4.04</v>
+        <v>4.26</v>
       </c>
       <c r="L1970">
-        <v>10.2</v>
+        <v>10.84</v>
       </c>
       <c r="M1970">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="N1970">
-        <v>10.3</v>
+        <v>10.76</v>
       </c>
       <c r="O1970">
         <v>0</v>
       </c>
       <c r="P1970" t="s">
-        <v>356</v>
+        <v>805</v>
       </c>
     </row>
     <row r="1971" spans="1:16">
       <c r="A1971" s="1">
+        <v>3</v>
+      </c>
+      <c r="B1971" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1971">
+        <v>-2.214689029841217</v>
+      </c>
+      <c r="D1971" t="s">
+        <v>384</v>
+      </c>
+      <c r="E1971">
+        <v>-2.238548167383255</v>
+      </c>
+      <c r="F1971">
+        <v>-1</v>
+      </c>
+      <c r="G1971">
+        <v>0.02261468902984122</v>
+      </c>
+      <c r="H1971">
+        <v>0.02375854816738325</v>
+      </c>
+      <c r="I1971">
+        <v>0.02385913754203806</v>
+      </c>
+      <c r="J1971">
+        <v>3.072942829168618</v>
+      </c>
+      <c r="K1971">
+        <v>4.04</v>
+      </c>
+      <c r="L1971">
+        <v>10.2</v>
+      </c>
+      <c r="M1971">
+        <v>4.23</v>
+      </c>
+      <c r="N1971">
+        <v>10.76</v>
+      </c>
+      <c r="O1971">
         <v>0</v>
       </c>
-      <c r="B1971" t="s">
-        <v>372</v>
-      </c>
-      <c r="C1971">
-        <v>-2.38649862556451</v>
-      </c>
-      <c r="D1971" t="s">
-        <v>360</v>
-      </c>
-      <c r="E1971">
-        <v>-1.931038680541931</v>
-      </c>
-      <c r="F1971">
-        <v>1</v>
-      </c>
-      <c r="G1971">
-        <v>0.02538649862556451</v>
-      </c>
-      <c r="H1971">
-        <v>0.02473103868054193</v>
-      </c>
-      <c r="I1971">
-        <v>0.4554599450225787</v>
-      </c>
-      <c r="J1971">
-        <v>2.923473394855686</v>
-      </c>
-      <c r="K1971">
-        <v>4.75</v>
-      </c>
-      <c r="L1971">
-        <v>11.5</v>
-      </c>
-      <c r="M1971">
-        <v>4.56</v>
-      </c>
-      <c r="N1971">
-        <v>11.4</v>
-      </c>
-      <c r="O1971">
-        <v>1</v>
-      </c>
       <c r="P1971" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="1972" spans="1:16">
       <c r="A1972" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1972" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C1972">
-        <v>-1.624761928136666</v>
+        <v>-3.040827059344563</v>
       </c>
       <c r="D1972" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="E1972">
-        <v>-1.569301983114086</v>
+        <v>-2.559193976970782</v>
       </c>
       <c r="F1972">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1972">
-        <v>0.02322476192813666</v>
+        <v>0.02604082705934457</v>
       </c>
       <c r="H1972">
-        <v>0.02216930198311409</v>
+        <v>0.02535919397697078</v>
       </c>
       <c r="I1972">
-        <v>-0.05545994502258011</v>
+        <v>0.4816330823737811</v>
       </c>
       <c r="J1972">
-        <v>2.923473394855686</v>
+        <v>3.061226749335697</v>
       </c>
       <c r="K1972">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="L1972">
-        <v>10.8</v>
+        <v>11.5</v>
       </c>
       <c r="M1972">
-        <v>4.06</v>
+        <v>4.56</v>
       </c>
       <c r="N1972">
-        <v>10.3</v>
+        <v>11.4</v>
       </c>
       <c r="O1972">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1972" t="s">
-        <v>806</v>
+        <v>356</v>
       </c>
     </row>
     <row r="1973" spans="1:16">
       <c r="A1973" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1973" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C1973">
-        <v>-1.613996662085224</v>
+        <v>-2.16082595217007</v>
       </c>
       <c r="D1973" t="s">
         <v>384</v>
       </c>
       <c r="E1973">
-        <v>-1.569301983114086</v>
+        <v>-2.188989149690002</v>
       </c>
       <c r="F1973">
         <v>-1</v>
       </c>
       <c r="G1973">
-        <v>0.02329399666208522</v>
+        <v>0.02392082595217007</v>
       </c>
       <c r="H1973">
-        <v>0.02216930198311409</v>
+        <v>0.02370898914969</v>
       </c>
       <c r="I1973">
-        <v>-0.04469467897113866</v>
+        <v>0.02816319751993213</v>
       </c>
       <c r="J1973">
-        <v>2.923473394855686</v>
+        <v>3.061226749335697</v>
       </c>
       <c r="K1973">
         <v>4.26</v>
       </c>
       <c r="L1973">
-        <v>10.84</v>
+        <v>10.88</v>
       </c>
       <c r="M1973">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="N1973">
-        <v>10.3</v>
+        <v>10.76</v>
       </c>
       <c r="O1973">
         <v>0</v>
       </c>
       <c r="P1973" t="s">
-        <v>806</v>
+        <v>356</v>
       </c>
     </row>
     <row r="1974" spans="1:16">
       <c r="A1974" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1974" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C1974">
-        <v>-1.610832515216973</v>
+        <v>-2.200825952170071</v>
       </c>
       <c r="D1974" t="s">
         <v>384</v>
       </c>
       <c r="E1974">
-        <v>-1.569301983114086</v>
+        <v>-2.188989149690002</v>
       </c>
       <c r="F1974">
         <v>-1</v>
       </c>
       <c r="G1974">
-        <v>0.02201083251521697</v>
+        <v>0.02388082595217007</v>
       </c>
       <c r="H1974">
-        <v>0.02216930198311409</v>
+        <v>0.02370898914969</v>
       </c>
       <c r="I1974">
-        <v>-0.04153053210288782</v>
+        <v>-0.0118368024800688</v>
       </c>
       <c r="J1974">
-        <v>2.923473394855686</v>
+        <v>3.061226749335697</v>
       </c>
       <c r="K1974">
-        <v>4.04</v>
+        <v>4.26</v>
       </c>
       <c r="L1974">
-        <v>10.2</v>
+        <v>10.84</v>
       </c>
       <c r="M1974">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="N1974">
-        <v>10.3</v>
+        <v>10.76</v>
       </c>
       <c r="O1974">
         <v>0</v>
       </c>
       <c r="P1974" t="s">
-        <v>806</v>
+        <v>356</v>
       </c>
     </row>
     <row r="1975" spans="1:16">
       <c r="A1975" s="1">
+        <v>3</v>
+      </c>
+      <c r="B1975" t="s">
+        <v>370</v>
+      </c>
+      <c r="C1975">
+        <v>-2.167356067316218</v>
+      </c>
+      <c r="D1975" t="s">
+        <v>384</v>
+      </c>
+      <c r="E1975">
+        <v>-2.188989149690002</v>
+      </c>
+      <c r="F1975">
+        <v>-1</v>
+      </c>
+      <c r="G1975">
+        <v>0.02256735606731622</v>
+      </c>
+      <c r="H1975">
+        <v>0.02370898914969</v>
+      </c>
+      <c r="I1975">
+        <v>0.02163308237378381</v>
+      </c>
+      <c r="J1975">
+        <v>3.061226749335697</v>
+      </c>
+      <c r="K1975">
+        <v>4.04</v>
+      </c>
+      <c r="L1975">
+        <v>10.2</v>
+      </c>
+      <c r="M1975">
+        <v>4.23</v>
+      </c>
+      <c r="N1975">
+        <v>10.76</v>
+      </c>
+      <c r="O1975">
         <v>0</v>
       </c>
-      <c r="B1975" t="s">
-        <v>372</v>
-      </c>
-      <c r="C1975">
-        <v>-0.9711299006237706</v>
-      </c>
-      <c r="D1975" t="s">
-        <v>361</v>
-      </c>
-      <c r="E1975">
-        <v>-0.6247947252330253</v>
-      </c>
-      <c r="F1975">
-        <v>1</v>
-      </c>
-      <c r="G1975">
-        <v>0.02397112990062377</v>
-      </c>
-      <c r="H1975">
-        <v>0.02342479472523303</v>
-      </c>
-      <c r="I1975">
-        <v>0.3463351753907453</v>
-      </c>
-      <c r="J1975">
-        <v>2.625501031710268</v>
-      </c>
-      <c r="K1975">
-        <v>4.75</v>
-      </c>
-      <c r="L1975">
-        <v>11.5</v>
-      </c>
-      <c r="M1975">
-        <v>4.58</v>
-      </c>
-      <c r="N1975">
-        <v>11.4</v>
-      </c>
-      <c r="O1975">
-        <v>1</v>
-      </c>
       <c r="P1975" t="s">
-        <v>618</v>
+        <v>356</v>
       </c>
     </row>
     <row r="1976" spans="1:16">
       <c r="A1976" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1976" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="C1976">
-        <v>-0.8973047458672312</v>
+        <v>-2.38649862556451</v>
       </c>
       <c r="D1976" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E1976">
-        <v>-0.6247947252330253</v>
+        <v>-1.931038680541931</v>
       </c>
       <c r="F1976">
         <v>1</v>
       </c>
       <c r="G1976">
-        <v>0.02325730474586723</v>
+        <v>0.02538649862556451</v>
       </c>
       <c r="H1976">
-        <v>0.02342479472523303</v>
+        <v>0.02473103868054193</v>
       </c>
       <c r="I1976">
-        <v>0.2725100206342059</v>
+        <v>0.4554599450225787</v>
       </c>
       <c r="J1976">
-        <v>2.625501031710268</v>
+        <v>2.923473394855686</v>
       </c>
       <c r="K1976">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="L1976">
-        <v>11.18</v>
+        <v>11.5</v>
       </c>
       <c r="M1976">
-        <v>4.58</v>
+        <v>4.56</v>
       </c>
       <c r="N1976">
         <v>11.4</v>
@@ -100455,204 +100464,204 @@
         <v>1</v>
       </c>
       <c r="P1976" t="s">
-        <v>618</v>
+        <v>806</v>
       </c>
     </row>
     <row r="1977" spans="1:16">
       <c r="A1977" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1977" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C1977">
-        <v>-0.9222446220619993</v>
+        <v>-1.573996662085223</v>
       </c>
       <c r="D1977" t="s">
-        <v>625</v>
+        <v>384</v>
       </c>
       <c r="E1977">
-        <v>-0.2321243744515353</v>
+        <v>-1.606292460239555</v>
       </c>
       <c r="F1977">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1977">
-        <v>0.022602244622062</v>
+        <v>0.02333399666208523</v>
       </c>
       <c r="H1977">
-        <v>0.02203212437445154</v>
+        <v>0.02312629246023955</v>
       </c>
       <c r="I1977">
-        <v>0.690120247610464</v>
+        <v>0.03229579815433148</v>
       </c>
       <c r="J1977">
-        <v>2.625501031710268</v>
+        <v>2.923473394855686</v>
       </c>
       <c r="K1977">
-        <v>4.48</v>
+        <v>4.26</v>
       </c>
       <c r="L1977">
-        <v>10.84</v>
+        <v>10.88</v>
       </c>
       <c r="M1977">
-        <v>4.24</v>
+        <v>4.23</v>
       </c>
       <c r="N1977">
-        <v>10.9</v>
+        <v>10.76</v>
       </c>
       <c r="O1977">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P1977" t="s">
-        <v>618</v>
+        <v>806</v>
       </c>
     </row>
     <row r="1978" spans="1:16">
       <c r="A1978" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1978" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C1978">
-        <v>-0.3583793847686358</v>
+        <v>-1.529353524445327</v>
       </c>
       <c r="D1978" t="s">
         <v>384</v>
       </c>
       <c r="E1978">
-        <v>-0.3595341887436856</v>
+        <v>-1.606292460239555</v>
       </c>
       <c r="F1978">
         <v>-1</v>
       </c>
       <c r="G1978">
-        <v>0.02195837938476864</v>
+        <v>0.02296935352444533</v>
       </c>
       <c r="H1978">
-        <v>0.02095953418874369</v>
+        <v>0.02312629246023955</v>
       </c>
       <c r="I1978">
-        <v>0.001154803975049745</v>
+        <v>0.07693893579422806</v>
       </c>
       <c r="J1978">
-        <v>2.625501031710268</v>
+        <v>2.923473394855686</v>
       </c>
       <c r="K1978">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="L1978">
-        <v>10.8</v>
+        <v>10.72</v>
       </c>
       <c r="M1978">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="N1978">
-        <v>10.3</v>
+        <v>10.76</v>
       </c>
       <c r="O1978">
         <v>0</v>
       </c>
       <c r="P1978" t="s">
-        <v>618</v>
+        <v>806</v>
       </c>
     </row>
     <row r="1979" spans="1:16">
       <c r="A1979" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1979" t="s">
         <v>370</v>
       </c>
       <c r="C1979">
-        <v>-0.3446343950857393</v>
+        <v>-1.610832515216973</v>
       </c>
       <c r="D1979" t="s">
         <v>384</v>
       </c>
       <c r="E1979">
-        <v>-0.3595341887436856</v>
+        <v>-1.606292460239555</v>
       </c>
       <c r="F1979">
         <v>-1</v>
       </c>
       <c r="G1979">
-        <v>0.02202463439508574</v>
+        <v>0.02201083251521697</v>
       </c>
       <c r="H1979">
-        <v>0.02095953418874369</v>
+        <v>0.02312629246023955</v>
       </c>
       <c r="I1979">
-        <v>0.01489979365794625</v>
+        <v>-0.004540054977418606</v>
       </c>
       <c r="J1979">
-        <v>2.625501031710268</v>
+        <v>2.923473394855686</v>
       </c>
       <c r="K1979">
-        <v>4.26</v>
+        <v>4.04</v>
       </c>
       <c r="L1979">
-        <v>10.84</v>
+        <v>10.2</v>
       </c>
       <c r="M1979">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="N1979">
-        <v>10.3</v>
+        <v>10.76</v>
       </c>
       <c r="O1979">
         <v>0</v>
       </c>
       <c r="P1979" t="s">
-        <v>618</v>
+        <v>806</v>
       </c>
     </row>
     <row r="1980" spans="1:16">
       <c r="A1980" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B1980" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="C1980">
-        <v>-0.2882591371581729</v>
+        <v>-0.9711299006237706</v>
       </c>
       <c r="D1980" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="E1980">
-        <v>-0.3595341887436856</v>
+        <v>-0.5722847045988217</v>
       </c>
       <c r="F1980">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1980">
-        <v>0.02076825913715817</v>
+        <v>0.02397112990062377</v>
       </c>
       <c r="H1980">
-        <v>0.02095953418874369</v>
+        <v>0.02337228470459882</v>
       </c>
       <c r="I1980">
-        <v>0.07127505158551273</v>
+        <v>0.3988451960249488</v>
       </c>
       <c r="J1980">
         <v>2.625501031710268</v>
       </c>
       <c r="K1980">
-        <v>4.01</v>
+        <v>4.75</v>
       </c>
       <c r="L1980">
-        <v>10.24</v>
+        <v>11.5</v>
       </c>
       <c r="M1980">
-        <v>4.06</v>
+        <v>4.56</v>
       </c>
       <c r="N1980">
-        <v>10.3</v>
+        <v>11.4</v>
       </c>
       <c r="O1980">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1980" t="s">
         <v>618</v>
@@ -100660,43 +100669,43 @@
     </row>
     <row r="1981" spans="1:16">
       <c r="A1981" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1981" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C1981">
-        <v>0.1722390805860297</v>
+        <v>-0.8810898180869486</v>
       </c>
       <c r="D1981" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E1981">
-        <v>0.4776536819124235</v>
+        <v>-0.5722847045988217</v>
       </c>
       <c r="F1981">
         <v>1</v>
       </c>
       <c r="G1981">
-        <v>0.02282776091941397</v>
+        <v>0.02364108981808695</v>
       </c>
       <c r="H1981">
-        <v>0.02232234631808758</v>
+        <v>0.02337228470459882</v>
       </c>
       <c r="I1981">
-        <v>0.3054146013263939</v>
+        <v>0.3088051134881269</v>
       </c>
       <c r="J1981">
-        <v>2.384791772508204</v>
+        <v>2.625501031710268</v>
       </c>
       <c r="K1981">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="L1981">
-        <v>11.5</v>
+        <v>11.38</v>
       </c>
       <c r="M1981">
-        <v>4.58</v>
+        <v>4.56</v>
       </c>
       <c r="N1981">
         <v>11.4</v>
@@ -100705,39 +100714,39 @@
         <v>1</v>
       </c>
       <c r="P1981" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="1982" spans="1:16">
       <c r="A1982" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1982" t="s">
         <v>374</v>
       </c>
       <c r="C1982">
-        <v>0.1561328591632432</v>
+        <v>-0.9222446220619993</v>
       </c>
       <c r="D1982" t="s">
         <v>625</v>
       </c>
       <c r="E1982">
-        <v>0.7884828845652123</v>
+        <v>-0.2321243744515353</v>
       </c>
       <c r="F1982">
         <v>1</v>
       </c>
       <c r="G1982">
-        <v>0.02152386714083676</v>
+        <v>0.022602244622062</v>
       </c>
       <c r="H1982">
-        <v>0.02101151711543479</v>
+        <v>0.02203212437445154</v>
       </c>
       <c r="I1982">
-        <v>0.6323500254019692</v>
+        <v>0.690120247610464</v>
       </c>
       <c r="J1982">
-        <v>2.384791772508204</v>
+        <v>2.625501031710268</v>
       </c>
       <c r="K1982">
         <v>4.48</v>
@@ -100755,39 +100764,39 @@
         <v>1</v>
       </c>
       <c r="P1982" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="1983" spans="1:16">
       <c r="A1983" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B1983" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C1983">
-        <v>0.7207870491150512</v>
+        <v>-0.3046343950857384</v>
       </c>
       <c r="D1983" t="s">
         <v>384</v>
       </c>
       <c r="E1983">
-        <v>0.6177454036166914</v>
+        <v>-0.3458693641344333</v>
       </c>
       <c r="F1983">
         <v>-1</v>
       </c>
       <c r="G1983">
-        <v>0.02103921295088495</v>
+        <v>0.02206463439508574</v>
       </c>
       <c r="H1983">
-        <v>0.01998225459638331</v>
+        <v>0.02186586936413443</v>
       </c>
       <c r="I1983">
-        <v>0.1030416454983598</v>
+        <v>0.04123496904869484</v>
       </c>
       <c r="J1983">
-        <v>2.384791772508204</v>
+        <v>2.625501031710268</v>
       </c>
       <c r="K1983">
         <v>4.26</v>
@@ -100796,48 +100805,48 @@
         <v>10.88</v>
       </c>
       <c r="M1983">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="N1983">
-        <v>10.3</v>
+        <v>10.76</v>
       </c>
       <c r="O1983">
         <v>0</v>
       </c>
       <c r="P1983" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="1984" spans="1:16">
       <c r="A1984" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B1984" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C1984">
-        <v>0.6807870491150503</v>
+        <v>-0.3446343950857393</v>
       </c>
       <c r="D1984" t="s">
         <v>384</v>
       </c>
       <c r="E1984">
-        <v>0.6177454036166914</v>
+        <v>-0.3458693641344333</v>
       </c>
       <c r="F1984">
         <v>-1</v>
       </c>
       <c r="G1984">
-        <v>0.02099921295088495</v>
+        <v>0.02202463439508574</v>
       </c>
       <c r="H1984">
-        <v>0.01998225459638331</v>
+        <v>0.02186586936413443</v>
       </c>
       <c r="I1984">
-        <v>0.06304164549835889</v>
+        <v>0.001234969048693912</v>
       </c>
       <c r="J1984">
-        <v>2.384791772508204</v>
+        <v>2.625501031710268</v>
       </c>
       <c r="K1984">
         <v>4.26</v>
@@ -100846,48 +100855,48 @@
         <v>10.84</v>
       </c>
       <c r="M1984">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="N1984">
-        <v>10.3</v>
+        <v>10.76</v>
       </c>
       <c r="O1984">
         <v>0</v>
       </c>
       <c r="P1984" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="1985" spans="1:16">
       <c r="A1985" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B1985" t="s">
         <v>375</v>
       </c>
       <c r="C1985">
-        <v>0.676984992242101</v>
+        <v>-0.2882591371581729</v>
       </c>
       <c r="D1985" t="s">
         <v>384</v>
       </c>
       <c r="E1985">
-        <v>0.6177454036166914</v>
+        <v>-0.3458693641344333</v>
       </c>
       <c r="F1985">
         <v>-1</v>
       </c>
       <c r="G1985">
-        <v>0.0198030150077579</v>
+        <v>0.02076825913715817</v>
       </c>
       <c r="H1985">
-        <v>0.01998225459638331</v>
+        <v>0.02186586936413443</v>
       </c>
       <c r="I1985">
-        <v>0.05923958862540957</v>
+        <v>0.05761022697626039</v>
       </c>
       <c r="J1985">
-        <v>2.384791772508204</v>
+        <v>2.625501031710268</v>
       </c>
       <c r="K1985">
         <v>4.01</v>
@@ -100896,404 +100905,404 @@
         <v>10.24</v>
       </c>
       <c r="M1985">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="N1985">
-        <v>10.3</v>
+        <v>10.76</v>
       </c>
       <c r="O1985">
         <v>0</v>
       </c>
       <c r="P1985" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="1986" spans="1:16">
       <c r="A1986" s="1">
+        <v>6</v>
+      </c>
+      <c r="B1986" t="s">
+        <v>376</v>
+      </c>
+      <c r="C1986">
+        <v>-0.3345943125489175</v>
+      </c>
+      <c r="D1986" t="s">
+        <v>384</v>
+      </c>
+      <c r="E1986">
+        <v>-0.3458693641344333</v>
+      </c>
+      <c r="F1986">
+        <v>-1</v>
+      </c>
+      <c r="G1986">
+        <v>0.02161459431254892</v>
+      </c>
+      <c r="H1986">
+        <v>0.02186586936413443</v>
+      </c>
+      <c r="I1986">
+        <v>0.01127505158551578</v>
+      </c>
+      <c r="J1986">
+        <v>2.625501031710268</v>
+      </c>
+      <c r="K1986">
+        <v>4.18</v>
+      </c>
+      <c r="L1986">
+        <v>10.64</v>
+      </c>
+      <c r="M1986">
+        <v>4.23</v>
+      </c>
+      <c r="N1986">
+        <v>10.76</v>
+      </c>
+      <c r="O1986">
         <v>0</v>
       </c>
-      <c r="B1986" t="s">
-        <v>372</v>
-      </c>
-      <c r="C1986">
-        <v>1.137917571557544</v>
-      </c>
-      <c r="D1986" t="s">
-        <v>361</v>
-      </c>
-      <c r="E1986">
-        <v>1.408771047943906</v>
-      </c>
-      <c r="F1986">
-        <v>1</v>
-      </c>
-      <c r="G1986">
-        <v>0.02186208242844246</v>
-      </c>
-      <c r="H1986">
-        <v>0.0213912289520561</v>
-      </c>
-      <c r="I1986">
-        <v>0.2708534763863621</v>
-      </c>
-      <c r="J1986">
-        <v>2.181491037566833</v>
-      </c>
-      <c r="K1986">
-        <v>4.75</v>
-      </c>
-      <c r="L1986">
-        <v>11.5</v>
-      </c>
-      <c r="M1986">
-        <v>4.58</v>
-      </c>
-      <c r="N1986">
-        <v>11.4</v>
-      </c>
-      <c r="O1986">
-        <v>1</v>
-      </c>
       <c r="P1986" t="s">
-        <v>357</v>
+        <v>618</v>
       </c>
     </row>
     <row r="1987" spans="1:16">
       <c r="A1987" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1987" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C1987">
-        <v>1.06692015170059</v>
+        <v>0.1722390805860297</v>
       </c>
       <c r="D1987" t="s">
-        <v>625</v>
+        <v>361</v>
       </c>
       <c r="E1987">
-        <v>1.65047800071663</v>
+        <v>0.4776536819124235</v>
       </c>
       <c r="F1987">
         <v>1</v>
       </c>
       <c r="G1987">
-        <v>0.02061307984829941</v>
+        <v>0.02282776091941397</v>
       </c>
       <c r="H1987">
-        <v>0.02014952199928337</v>
+        <v>0.02232234631808758</v>
       </c>
       <c r="I1987">
-        <v>0.5835578490160405</v>
+        <v>0.3054146013263939</v>
       </c>
       <c r="J1987">
-        <v>2.181491037566833</v>
+        <v>2.384791772508204</v>
       </c>
       <c r="K1987">
-        <v>4.48</v>
+        <v>4.75</v>
       </c>
       <c r="L1987">
-        <v>10.84</v>
+        <v>11.5</v>
       </c>
       <c r="M1987">
-        <v>4.24</v>
+        <v>4.58</v>
       </c>
       <c r="N1987">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="O1987">
         <v>1</v>
       </c>
       <c r="P1987" t="s">
-        <v>357</v>
+        <v>619</v>
       </c>
     </row>
     <row r="1988" spans="1:16">
       <c r="A1988" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1988" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C1988">
-        <v>1.586848179965294</v>
+        <v>0.1561328591632432</v>
       </c>
       <c r="D1988" t="s">
-        <v>384</v>
+        <v>625</v>
       </c>
       <c r="E1988">
-        <v>1.443146387478661</v>
+        <v>0.7884828845652123</v>
       </c>
       <c r="F1988">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1988">
-        <v>0.02017315182003471</v>
+        <v>0.02152386714083676</v>
       </c>
       <c r="H1988">
-        <v>0.01915685361252134</v>
+        <v>0.02101151711543479</v>
       </c>
       <c r="I1988">
-        <v>0.1437017924866328</v>
+        <v>0.6323500254019692</v>
       </c>
       <c r="J1988">
-        <v>2.181491037566833</v>
+        <v>2.384791772508204</v>
       </c>
       <c r="K1988">
-        <v>4.26</v>
+        <v>4.48</v>
       </c>
       <c r="L1988">
-        <v>10.88</v>
+        <v>10.84</v>
       </c>
       <c r="M1988">
-        <v>4.06</v>
+        <v>4.24</v>
       </c>
       <c r="N1988">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="O1988">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1988" t="s">
-        <v>357</v>
+        <v>619</v>
       </c>
     </row>
     <row r="1989" spans="1:16">
       <c r="A1989" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1989" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C1989">
-        <v>1.546848179965293</v>
+        <v>0.7207870491150512</v>
       </c>
       <c r="D1989" t="s">
         <v>384</v>
       </c>
       <c r="E1989">
-        <v>1.443146387478661</v>
+        <v>0.6723308022902934</v>
       </c>
       <c r="F1989">
         <v>-1</v>
       </c>
       <c r="G1989">
-        <v>0.02013315182003471</v>
+        <v>0.02103921295088495</v>
       </c>
       <c r="H1989">
-        <v>0.01915685361252134</v>
+        <v>0.02084766919770971</v>
       </c>
       <c r="I1989">
-        <v>0.1037017924866319</v>
+        <v>0.0484562468247578</v>
       </c>
       <c r="J1989">
-        <v>2.181491037566833</v>
+        <v>2.384791772508204</v>
       </c>
       <c r="K1989">
         <v>4.26</v>
       </c>
       <c r="L1989">
-        <v>10.84</v>
+        <v>10.88</v>
       </c>
       <c r="M1989">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="N1989">
-        <v>10.3</v>
+        <v>10.76</v>
       </c>
       <c r="O1989">
         <v>0</v>
       </c>
       <c r="P1989" t="s">
-        <v>357</v>
+        <v>619</v>
       </c>
     </row>
     <row r="1990" spans="1:16">
       <c r="A1990" s="1">
+        <v>3</v>
+      </c>
+      <c r="B1990" t="s">
+        <v>367</v>
+      </c>
+      <c r="C1990">
+        <v>0.6807870491150503</v>
+      </c>
+      <c r="D1990" t="s">
+        <v>384</v>
+      </c>
+      <c r="E1990">
+        <v>0.6723308022902934</v>
+      </c>
+      <c r="F1990">
+        <v>-1</v>
+      </c>
+      <c r="G1990">
+        <v>0.02099921295088495</v>
+      </c>
+      <c r="H1990">
+        <v>0.02084766919770971</v>
+      </c>
+      <c r="I1990">
+        <v>0.008456246824756875</v>
+      </c>
+      <c r="J1990">
+        <v>2.384791772508204</v>
+      </c>
+      <c r="K1990">
+        <v>4.26</v>
+      </c>
+      <c r="L1990">
+        <v>10.84</v>
+      </c>
+      <c r="M1990">
+        <v>4.23</v>
+      </c>
+      <c r="N1990">
+        <v>10.76</v>
+      </c>
+      <c r="O1990">
         <v>0</v>
       </c>
-      <c r="B1990" t="s">
-        <v>372</v>
-      </c>
-      <c r="C1990">
-        <v>1.243880896429898</v>
-      </c>
-      <c r="D1990" t="s">
-        <v>361</v>
-      </c>
-      <c r="E1990">
-        <v>1.510942001189248</v>
-      </c>
-      <c r="F1990">
-        <v>1</v>
-      </c>
-      <c r="G1990">
-        <v>0.0217561191035701</v>
-      </c>
-      <c r="H1990">
-        <v>0.02128905799881076</v>
-      </c>
-      <c r="I1990">
-        <v>0.2670611047593496</v>
-      </c>
-      <c r="J1990">
-        <v>2.159182969172653</v>
-      </c>
-      <c r="K1990">
-        <v>4.75</v>
-      </c>
-      <c r="L1990">
-        <v>11.5</v>
-      </c>
-      <c r="M1990">
-        <v>4.58</v>
-      </c>
-      <c r="N1990">
-        <v>11.4</v>
-      </c>
-      <c r="O1990">
-        <v>1</v>
-      </c>
       <c r="P1990" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="1991" spans="1:16">
       <c r="A1991" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1991" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C1991">
-        <v>1.166860298106513</v>
+        <v>1.137917571557544</v>
       </c>
       <c r="D1991" t="s">
-        <v>625</v>
+        <v>361</v>
       </c>
       <c r="E1991">
-        <v>1.74506421070795</v>
+        <v>1.408771047943906</v>
       </c>
       <c r="F1991">
         <v>1</v>
       </c>
       <c r="G1991">
-        <v>0.02051313970189349</v>
+        <v>0.02186208242844246</v>
       </c>
       <c r="H1991">
-        <v>0.02005493578929205</v>
+        <v>0.0213912289520561</v>
       </c>
       <c r="I1991">
-        <v>0.5782039126014364</v>
+        <v>0.2708534763863621</v>
       </c>
       <c r="J1991">
-        <v>2.159182969172653</v>
+        <v>2.181491037566833</v>
       </c>
       <c r="K1991">
-        <v>4.48</v>
+        <v>4.75</v>
       </c>
       <c r="L1991">
-        <v>10.84</v>
+        <v>11.5</v>
       </c>
       <c r="M1991">
-        <v>4.24</v>
+        <v>4.58</v>
       </c>
       <c r="N1991">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="O1991">
         <v>1</v>
       </c>
       <c r="P1991" t="s">
-        <v>622</v>
+        <v>357</v>
       </c>
     </row>
     <row r="1992" spans="1:16">
       <c r="A1992" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1992" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C1992">
-        <v>1.681880551324499</v>
+        <v>1.06692015170059</v>
       </c>
       <c r="D1992" t="s">
-        <v>371</v>
+        <v>625</v>
       </c>
       <c r="E1992">
-        <v>1.476900804542481</v>
+        <v>1.65047800071663</v>
       </c>
       <c r="F1992">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1992">
-        <v>0.0200781194486755</v>
+        <v>0.02061307984829941</v>
       </c>
       <c r="H1992">
-        <v>0.01892309919545752</v>
+        <v>0.02014952199928337</v>
       </c>
       <c r="I1992">
-        <v>0.2049797467820174</v>
+        <v>0.5835578490160405</v>
       </c>
       <c r="J1992">
-        <v>2.159182969172653</v>
+        <v>2.181491037566833</v>
       </c>
       <c r="K1992">
-        <v>4.26</v>
+        <v>4.48</v>
       </c>
       <c r="L1992">
-        <v>10.88</v>
+        <v>10.84</v>
       </c>
       <c r="M1992">
-        <v>4.04</v>
+        <v>4.24</v>
       </c>
       <c r="N1992">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
       <c r="O1992">
         <v>1</v>
       </c>
       <c r="P1992" t="s">
-        <v>622</v>
+        <v>357</v>
       </c>
     </row>
     <row r="1993" spans="1:16">
       <c r="A1993" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1993" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C1993">
-        <v>1.673023359166583</v>
+        <v>1.586848179965294</v>
       </c>
       <c r="D1993" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E1993">
-        <v>1.476900804542481</v>
+        <v>1.386776208229996</v>
       </c>
       <c r="F1993">
         <v>-1</v>
       </c>
       <c r="G1993">
-        <v>0.01976697664083342</v>
+        <v>0.02017315182003471</v>
       </c>
       <c r="H1993">
-        <v>0.01892309919545752</v>
+        <v>0.01901322379177</v>
       </c>
       <c r="I1993">
-        <v>0.1961225546241021</v>
+        <v>0.2000719717352979</v>
       </c>
       <c r="J1993">
-        <v>2.159182969172653</v>
+        <v>2.181491037566833</v>
       </c>
       <c r="K1993">
-        <v>4.19</v>
+        <v>4.26</v>
       </c>
       <c r="L1993">
-        <v>10.72</v>
+        <v>10.88</v>
       </c>
       <c r="M1993">
         <v>4.04</v>
@@ -101305,795 +101314,795 @@
         <v>1</v>
       </c>
       <c r="P1993" t="s">
-        <v>622</v>
+        <v>357</v>
       </c>
     </row>
     <row r="1994" spans="1:16">
       <c r="A1994" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1994" t="s">
         <v>372</v>
       </c>
       <c r="C1994">
-        <v>0.8761599758225351</v>
+        <v>1.579552552594972</v>
       </c>
       <c r="D1994" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="E1994">
-        <v>1.156381618793098</v>
+        <v>1.386776208229996</v>
       </c>
       <c r="F1994">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1994">
-        <v>0.02212384002417746</v>
+        <v>0.01986044744740503</v>
       </c>
       <c r="H1994">
-        <v>0.0216436183812069</v>
+        <v>0.01901322379177</v>
       </c>
       <c r="I1994">
-        <v>0.2802216429705631</v>
+        <v>0.1927763443649759</v>
       </c>
       <c r="J1994">
-        <v>2.236597899826835</v>
+        <v>2.181491037566833</v>
       </c>
       <c r="K1994">
-        <v>4.75</v>
+        <v>4.19</v>
       </c>
       <c r="L1994">
-        <v>11.5</v>
+        <v>10.72</v>
       </c>
       <c r="M1994">
-        <v>4.58</v>
+        <v>4.04</v>
       </c>
       <c r="N1994">
-        <v>11.4</v>
+        <v>10.2</v>
       </c>
       <c r="O1994">
         <v>1</v>
       </c>
       <c r="P1994" t="s">
-        <v>807</v>
+        <v>357</v>
       </c>
     </row>
     <row r="1995" spans="1:16">
       <c r="A1995" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1995" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C1995">
-        <v>0.820041408775781</v>
+        <v>1.243880896429898</v>
       </c>
       <c r="D1995" t="s">
-        <v>625</v>
+        <v>361</v>
       </c>
       <c r="E1995">
-        <v>1.416824904734222</v>
+        <v>1.510942001189248</v>
       </c>
       <c r="F1995">
         <v>1</v>
       </c>
       <c r="G1995">
-        <v>0.02085995859122422</v>
+        <v>0.0217561191035701</v>
       </c>
       <c r="H1995">
-        <v>0.02038317509526578</v>
+        <v>0.02128905799881076</v>
       </c>
       <c r="I1995">
-        <v>0.5967834959584408</v>
+        <v>0.2670611047593496</v>
       </c>
       <c r="J1995">
-        <v>2.236597899826835</v>
+        <v>2.159182969172653</v>
       </c>
       <c r="K1995">
-        <v>4.48</v>
+        <v>4.75</v>
       </c>
       <c r="L1995">
-        <v>10.84</v>
+        <v>11.5</v>
       </c>
       <c r="M1995">
-        <v>4.24</v>
+        <v>4.58</v>
       </c>
       <c r="N1995">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="O1995">
         <v>1</v>
       </c>
       <c r="P1995" t="s">
-        <v>807</v>
+        <v>622</v>
       </c>
     </row>
     <row r="1996" spans="1:16">
       <c r="A1996" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1996" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C1996">
-        <v>1.352092946737686</v>
+        <v>1.166860298106513</v>
       </c>
       <c r="D1996" t="s">
-        <v>384</v>
+        <v>625</v>
       </c>
       <c r="E1996">
-        <v>1.219412526703053</v>
+        <v>1.74506421070795</v>
       </c>
       <c r="F1996">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G1996">
-        <v>0.02040790705326231</v>
+        <v>0.02051313970189349</v>
       </c>
       <c r="H1996">
-        <v>0.01938058747329695</v>
+        <v>0.02005493578929205</v>
       </c>
       <c r="I1996">
-        <v>0.1326804200346334</v>
+        <v>0.5782039126014364</v>
       </c>
       <c r="J1996">
-        <v>2.236597899826835</v>
+        <v>2.159182969172653</v>
       </c>
       <c r="K1996">
-        <v>4.26</v>
+        <v>4.48</v>
       </c>
       <c r="L1996">
-        <v>10.88</v>
+        <v>10.84</v>
       </c>
       <c r="M1996">
-        <v>4.06</v>
+        <v>4.24</v>
       </c>
       <c r="N1996">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="O1996">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1996" t="s">
-        <v>807</v>
+        <v>622</v>
       </c>
     </row>
     <row r="1997" spans="1:16">
       <c r="A1997" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1997" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C1997">
-        <v>1.348654799725564</v>
+        <v>1.681880551324499</v>
       </c>
       <c r="D1997" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="E1997">
-        <v>1.219412526703053</v>
+        <v>1.476900804542481</v>
       </c>
       <c r="F1997">
         <v>-1</v>
       </c>
       <c r="G1997">
-        <v>0.02009134520027444</v>
+        <v>0.0200781194486755</v>
       </c>
       <c r="H1997">
-        <v>0.01938058747329695</v>
+        <v>0.01892309919545752</v>
       </c>
       <c r="I1997">
-        <v>0.1292422730225109</v>
+        <v>0.2049797467820174</v>
       </c>
       <c r="J1997">
-        <v>2.236597899826835</v>
+        <v>2.159182969172653</v>
       </c>
       <c r="K1997">
-        <v>4.19</v>
+        <v>4.26</v>
       </c>
       <c r="L1997">
-        <v>10.72</v>
+        <v>10.88</v>
       </c>
       <c r="M1997">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="N1997">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="O1997">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P1997" t="s">
-        <v>807</v>
+        <v>622</v>
       </c>
     </row>
     <row r="1998" spans="1:16">
       <c r="A1998" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1998" t="s">
         <v>372</v>
       </c>
       <c r="C1998">
-        <v>0.9514043421892833</v>
+        <v>1.673023359166583</v>
       </c>
       <c r="D1998" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="E1998">
-        <v>1.228933028889879</v>
+        <v>1.476900804542481</v>
       </c>
       <c r="F1998">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G1998">
-        <v>0.02204859565781072</v>
+        <v>0.01976697664083342</v>
       </c>
       <c r="H1998">
-        <v>0.02157106697111012</v>
+        <v>0.01892309919545752</v>
       </c>
       <c r="I1998">
-        <v>0.2775286867005953</v>
+        <v>0.1961225546241021</v>
       </c>
       <c r="J1998">
-        <v>2.22075698059173</v>
+        <v>2.159182969172653</v>
       </c>
       <c r="K1998">
-        <v>4.75</v>
+        <v>4.19</v>
       </c>
       <c r="L1998">
-        <v>11.5</v>
+        <v>10.72</v>
       </c>
       <c r="M1998">
-        <v>4.58</v>
+        <v>4.04</v>
       </c>
       <c r="N1998">
-        <v>11.4</v>
+        <v>10.2</v>
       </c>
       <c r="O1998">
         <v>1</v>
       </c>
       <c r="P1998" t="s">
-        <v>808</v>
+        <v>622</v>
       </c>
     </row>
     <row r="1999" spans="1:16">
       <c r="A1999" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1999" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C1999">
-        <v>0.8910087269490496</v>
+        <v>0.8761599758225351</v>
       </c>
       <c r="D1999" t="s">
-        <v>625</v>
+        <v>361</v>
       </c>
       <c r="E1999">
-        <v>1.483990402291065</v>
+        <v>1.156381618793098</v>
       </c>
       <c r="F1999">
         <v>1</v>
       </c>
       <c r="G1999">
-        <v>0.02078899127305095</v>
+        <v>0.02212384002417746</v>
       </c>
       <c r="H1999">
-        <v>0.02031600959770893</v>
+        <v>0.0216436183812069</v>
       </c>
       <c r="I1999">
-        <v>0.5929816753420152</v>
+        <v>0.2802216429705631</v>
       </c>
       <c r="J1999">
-        <v>2.22075698059173</v>
+        <v>2.236597899826835</v>
       </c>
       <c r="K1999">
-        <v>4.48</v>
+        <v>4.75</v>
       </c>
       <c r="L1999">
-        <v>10.84</v>
+        <v>11.5</v>
       </c>
       <c r="M1999">
-        <v>4.24</v>
+        <v>4.58</v>
       </c>
       <c r="N1999">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="O1999">
         <v>1</v>
       </c>
       <c r="P1999" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="2000" spans="1:16">
       <c r="A2000" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2000" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C2000">
-        <v>1.419575262679233</v>
+        <v>0.820041408775781</v>
       </c>
       <c r="D2000" t="s">
-        <v>384</v>
+        <v>625</v>
       </c>
       <c r="E2000">
-        <v>1.283726658797578</v>
+        <v>1.416824904734222</v>
       </c>
       <c r="F2000">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2000">
-        <v>0.02034042473732077</v>
+        <v>0.02085995859122422</v>
       </c>
       <c r="H2000">
-        <v>0.01931627334120243</v>
+        <v>0.02038317509526578</v>
       </c>
       <c r="I2000">
-        <v>0.1358486038816551</v>
+        <v>0.5967834959584408</v>
       </c>
       <c r="J2000">
-        <v>2.22075698059173</v>
+        <v>2.236597899826835</v>
       </c>
       <c r="K2000">
-        <v>4.26</v>
+        <v>4.48</v>
       </c>
       <c r="L2000">
-        <v>10.88</v>
+        <v>10.84</v>
       </c>
       <c r="M2000">
-        <v>4.06</v>
+        <v>4.24</v>
       </c>
       <c r="N2000">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="O2000">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2000" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="2001" spans="1:16">
       <c r="A2001" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2001" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C2001">
-        <v>1.415028251320653</v>
+        <v>1.352092946737686</v>
       </c>
       <c r="D2001" t="s">
         <v>384</v>
       </c>
       <c r="E2001">
-        <v>1.283726658797578</v>
+        <v>1.299190883732489</v>
       </c>
       <c r="F2001">
         <v>-1</v>
       </c>
       <c r="G2001">
-        <v>0.02002497174867935</v>
+        <v>0.02040790705326231</v>
       </c>
       <c r="H2001">
-        <v>0.01931627334120243</v>
+        <v>0.02022080911626751</v>
       </c>
       <c r="I2001">
-        <v>0.1313015925230747</v>
+        <v>0.05290206300519706</v>
       </c>
       <c r="J2001">
-        <v>2.22075698059173</v>
+        <v>2.236597899826835</v>
       </c>
       <c r="K2001">
-        <v>4.19</v>
+        <v>4.26</v>
       </c>
       <c r="L2001">
-        <v>10.72</v>
+        <v>10.88</v>
       </c>
       <c r="M2001">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="N2001">
-        <v>10.3</v>
+        <v>10.76</v>
       </c>
       <c r="O2001">
         <v>0</v>
       </c>
       <c r="P2001" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="2002" spans="1:16">
       <c r="A2002" s="1">
+        <v>3</v>
+      </c>
+      <c r="B2002" t="s">
+        <v>372</v>
+      </c>
+      <c r="C2002">
+        <v>1.348654799725564</v>
+      </c>
+      <c r="D2002" t="s">
+        <v>384</v>
+      </c>
+      <c r="E2002">
+        <v>1.299190883732489</v>
+      </c>
+      <c r="F2002">
+        <v>-1</v>
+      </c>
+      <c r="G2002">
+        <v>0.02009134520027444</v>
+      </c>
+      <c r="H2002">
+        <v>0.02022080911626751</v>
+      </c>
+      <c r="I2002">
+        <v>0.04946391599307454</v>
+      </c>
+      <c r="J2002">
+        <v>2.236597899826835</v>
+      </c>
+      <c r="K2002">
+        <v>4.19</v>
+      </c>
+      <c r="L2002">
+        <v>10.72</v>
+      </c>
+      <c r="M2002">
+        <v>4.23</v>
+      </c>
+      <c r="N2002">
+        <v>10.76</v>
+      </c>
+      <c r="O2002">
         <v>0</v>
       </c>
-      <c r="B2002" t="s">
-        <v>374</v>
-      </c>
-      <c r="C2002">
-        <v>1.116960939884411</v>
-      </c>
-      <c r="D2002" t="s">
-        <v>625</v>
-      </c>
-      <c r="E2002">
-        <v>1.697838032390603</v>
-      </c>
-      <c r="F2002">
-        <v>1</v>
-      </c>
-      <c r="G2002">
-        <v>0.02056303906011559</v>
-      </c>
-      <c r="H2002">
-        <v>0.0201021619676094</v>
-      </c>
-      <c r="I2002">
-        <v>0.5808770925061921</v>
-      </c>
-      <c r="J2002">
-        <v>2.170321218775801</v>
-      </c>
-      <c r="K2002">
-        <v>4.48</v>
-      </c>
-      <c r="L2002">
-        <v>10.84</v>
-      </c>
-      <c r="M2002">
-        <v>4.24</v>
-      </c>
-      <c r="N2002">
-        <v>10.9</v>
-      </c>
-      <c r="O2002">
-        <v>1</v>
-      </c>
       <c r="P2002" t="s">
-        <v>372</v>
+        <v>807</v>
       </c>
     </row>
     <row r="2003" spans="1:16">
       <c r="A2003" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2003" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="C2003">
-        <v>1.634431608015088</v>
+        <v>0.9514043421892833</v>
       </c>
       <c r="D2003" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="E2003">
-        <v>1.431902276145763</v>
+        <v>1.228933028889879</v>
       </c>
       <c r="F2003">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2003">
-        <v>0.02012556839198491</v>
+        <v>0.02204859565781072</v>
       </c>
       <c r="H2003">
-        <v>0.01896809772385424</v>
+        <v>0.02157106697111012</v>
       </c>
       <c r="I2003">
-        <v>0.2025293318693251</v>
+        <v>0.2775286867005953</v>
       </c>
       <c r="J2003">
-        <v>2.170321218775801</v>
+        <v>2.22075698059173</v>
       </c>
       <c r="K2003">
-        <v>4.26</v>
+        <v>4.75</v>
       </c>
       <c r="L2003">
-        <v>10.88</v>
+        <v>11.5</v>
       </c>
       <c r="M2003">
-        <v>4.04</v>
+        <v>4.58</v>
       </c>
       <c r="N2003">
-        <v>10.2</v>
+        <v>11.4</v>
       </c>
       <c r="O2003">
         <v>1</v>
       </c>
       <c r="P2003" t="s">
-        <v>372</v>
+        <v>808</v>
       </c>
     </row>
     <row r="2004" spans="1:16">
       <c r="A2004" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2004" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C2004">
-        <v>1.626354093329393</v>
+        <v>0.8910087269490496</v>
       </c>
       <c r="D2004" t="s">
-        <v>371</v>
+        <v>625</v>
       </c>
       <c r="E2004">
-        <v>1.431902276145763</v>
+        <v>1.483990402291065</v>
       </c>
       <c r="F2004">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2004">
-        <v>0.01981364590667061</v>
+        <v>0.02078899127305095</v>
       </c>
       <c r="H2004">
-        <v>0.01896809772385424</v>
+        <v>0.02031600959770893</v>
       </c>
       <c r="I2004">
-        <v>0.19445181718363</v>
+        <v>0.5929816753420152</v>
       </c>
       <c r="J2004">
-        <v>2.170321218775801</v>
+        <v>2.22075698059173</v>
       </c>
       <c r="K2004">
-        <v>4.19</v>
+        <v>4.48</v>
       </c>
       <c r="L2004">
-        <v>10.72</v>
+        <v>10.84</v>
       </c>
       <c r="M2004">
-        <v>4.04</v>
+        <v>4.24</v>
       </c>
       <c r="N2004">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
       <c r="O2004">
         <v>1</v>
       </c>
       <c r="P2004" t="s">
-        <v>372</v>
+        <v>808</v>
       </c>
     </row>
     <row r="2005" spans="1:16">
       <c r="A2005" s="1">
+        <v>2</v>
+      </c>
+      <c r="B2005" t="s">
+        <v>371</v>
+      </c>
+      <c r="C2005">
+        <v>1.419575262679233</v>
+      </c>
+      <c r="D2005" t="s">
+        <v>384</v>
+      </c>
+      <c r="E2005">
+        <v>1.366197972096982</v>
+      </c>
+      <c r="F2005">
+        <v>-1</v>
+      </c>
+      <c r="G2005">
+        <v>0.02034042473732077</v>
+      </c>
+      <c r="H2005">
+        <v>0.02015380202790302</v>
+      </c>
+      <c r="I2005">
+        <v>0.05337729058225094</v>
+      </c>
+      <c r="J2005">
+        <v>2.22075698059173</v>
+      </c>
+      <c r="K2005">
+        <v>4.26</v>
+      </c>
+      <c r="L2005">
+        <v>10.88</v>
+      </c>
+      <c r="M2005">
+        <v>4.23</v>
+      </c>
+      <c r="N2005">
+        <v>10.76</v>
+      </c>
+      <c r="O2005">
         <v>0</v>
       </c>
-      <c r="B2005" t="s">
-        <v>374</v>
-      </c>
-      <c r="C2005">
-        <v>1.362397924347944</v>
-      </c>
-      <c r="D2005" t="s">
-        <v>625</v>
-      </c>
-      <c r="E2005">
-        <v>1.930126606972163</v>
-      </c>
-      <c r="F2005">
-        <v>1</v>
-      </c>
-      <c r="G2005">
-        <v>0.02031760207565205</v>
-      </c>
-      <c r="H2005">
-        <v>0.01986987339302784</v>
-      </c>
-      <c r="I2005">
-        <v>0.5677286826242192</v>
-      </c>
-      <c r="J2005">
-        <v>2.115536177600905</v>
-      </c>
-      <c r="K2005">
-        <v>4.48</v>
-      </c>
-      <c r="L2005">
-        <v>10.84</v>
-      </c>
-      <c r="M2005">
-        <v>4.24</v>
-      </c>
-      <c r="N2005">
-        <v>10.9</v>
-      </c>
-      <c r="O2005">
-        <v>1</v>
-      </c>
       <c r="P2005" t="s">
-        <v>367</v>
+        <v>808</v>
       </c>
     </row>
     <row r="2006" spans="1:16">
       <c r="A2006" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2006" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C2006">
-        <v>1.867815883420144</v>
+        <v>1.415028251320653</v>
       </c>
       <c r="D2006" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="E2006">
-        <v>1.653233842492343</v>
+        <v>1.366197972096982</v>
       </c>
       <c r="F2006">
         <v>-1</v>
       </c>
       <c r="G2006">
-        <v>0.01989218411657986</v>
+        <v>0.02002497174867935</v>
       </c>
       <c r="H2006">
-        <v>0.01874676615750766</v>
+        <v>0.02015380202790302</v>
       </c>
       <c r="I2006">
-        <v>0.2145820409278016</v>
+        <v>0.04883027922367056</v>
       </c>
       <c r="J2006">
-        <v>2.115536177600905</v>
+        <v>2.22075698059173</v>
       </c>
       <c r="K2006">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="L2006">
-        <v>10.88</v>
+        <v>10.72</v>
       </c>
       <c r="M2006">
-        <v>4.04</v>
+        <v>4.23</v>
       </c>
       <c r="N2006">
-        <v>10.2</v>
+        <v>10.76</v>
       </c>
       <c r="O2006">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2006" t="s">
-        <v>367</v>
+        <v>808</v>
       </c>
     </row>
     <row r="2007" spans="1:16">
       <c r="A2007" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2007" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C2007">
-        <v>1.855903415852207</v>
+        <v>1.116960939884411</v>
       </c>
       <c r="D2007" t="s">
-        <v>371</v>
+        <v>625</v>
       </c>
       <c r="E2007">
-        <v>1.653233842492343</v>
+        <v>1.697838032390603</v>
       </c>
       <c r="F2007">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2007">
-        <v>0.01958409658414779</v>
+        <v>0.02056303906011559</v>
       </c>
       <c r="H2007">
-        <v>0.01874676615750766</v>
+        <v>0.0201021619676094</v>
       </c>
       <c r="I2007">
-        <v>0.2026695733598647</v>
+        <v>0.5808770925061921</v>
       </c>
       <c r="J2007">
-        <v>2.115536177600905</v>
+        <v>2.170321218775801</v>
       </c>
       <c r="K2007">
-        <v>4.19</v>
+        <v>4.48</v>
       </c>
       <c r="L2007">
-        <v>10.72</v>
+        <v>10.84</v>
       </c>
       <c r="M2007">
-        <v>4.04</v>
+        <v>4.24</v>
       </c>
       <c r="N2007">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
       <c r="O2007">
         <v>1</v>
       </c>
       <c r="P2007" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="2008" spans="1:16">
       <c r="A2008" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2008" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C2008">
-        <v>0.9665985078750996</v>
+        <v>1.634431608015088</v>
       </c>
       <c r="D2008" t="s">
-        <v>625</v>
+        <v>370</v>
       </c>
       <c r="E2008">
-        <v>1.555530730667506</v>
+        <v>1.431902276145763</v>
       </c>
       <c r="F2008">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2008">
-        <v>0.0207134014921249</v>
+        <v>0.02012556839198491</v>
       </c>
       <c r="H2008">
-        <v>0.02024446926933249</v>
+        <v>0.01896809772385424</v>
       </c>
       <c r="I2008">
-        <v>0.5889322227924065</v>
+        <v>0.2025293318693251</v>
       </c>
       <c r="J2008">
-        <v>2.203884261635022</v>
+        <v>2.170321218775801</v>
       </c>
       <c r="K2008">
-        <v>4.48</v>
+        <v>4.26</v>
       </c>
       <c r="L2008">
-        <v>10.84</v>
+        <v>10.88</v>
       </c>
       <c r="M2008">
-        <v>4.24</v>
+        <v>4.04</v>
       </c>
       <c r="N2008">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="O2008">
         <v>1</v>
       </c>
       <c r="P2008" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="2009" spans="1:16">
       <c r="A2009" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2009" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C2009">
-        <v>1.491453045434808</v>
+        <v>1.626354093329393</v>
       </c>
       <c r="D2009" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E2009">
-        <v>1.29630758299451</v>
+        <v>1.431902276145763</v>
       </c>
       <c r="F2009">
         <v>-1</v>
       </c>
       <c r="G2009">
-        <v>0.0202685469545652</v>
+        <v>0.01981364590667061</v>
       </c>
       <c r="H2009">
-        <v>0.01910369241700549</v>
+        <v>0.01896809772385424</v>
       </c>
       <c r="I2009">
-        <v>0.1951454624402977</v>
+        <v>0.19445181718363</v>
       </c>
       <c r="J2009">
-        <v>2.203884261635022</v>
+        <v>2.170321218775801</v>
       </c>
       <c r="K2009">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="L2009">
-        <v>10.88</v>
+        <v>10.72</v>
       </c>
       <c r="M2009">
         <v>4.04</v>
@@ -102105,101 +102114,101 @@
         <v>1</v>
       </c>
       <c r="P2009" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="2010" spans="1:16">
       <c r="A2010" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2010" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C2010">
-        <v>1.485724943749258</v>
+        <v>1.362397924347944</v>
       </c>
       <c r="D2010" t="s">
-        <v>371</v>
+        <v>625</v>
       </c>
       <c r="E2010">
-        <v>1.29630758299451</v>
+        <v>1.930126606972163</v>
       </c>
       <c r="F2010">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2010">
-        <v>0.01995427505625074</v>
+        <v>0.02031760207565205</v>
       </c>
       <c r="H2010">
-        <v>0.01910369241700549</v>
+        <v>0.01986987339302784</v>
       </c>
       <c r="I2010">
-        <v>0.1894173607547476</v>
+        <v>0.5677286826242192</v>
       </c>
       <c r="J2010">
-        <v>2.203884261635022</v>
+        <v>2.115536177600905</v>
       </c>
       <c r="K2010">
-        <v>4.19</v>
+        <v>4.48</v>
       </c>
       <c r="L2010">
-        <v>10.72</v>
+        <v>10.84</v>
       </c>
       <c r="M2010">
-        <v>4.04</v>
+        <v>4.24</v>
       </c>
       <c r="N2010">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
       <c r="O2010">
         <v>1</v>
       </c>
       <c r="P2010" t="s">
-        <v>364</v>
+        <v>809</v>
       </c>
     </row>
     <row r="2011" spans="1:16">
       <c r="A2011" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2011" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C2011">
-        <v>0.8629086413845322</v>
+        <v>1.867815883420144</v>
       </c>
       <c r="D2011" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="E2011">
-        <v>1.073492044502927</v>
+        <v>1.653233842492343</v>
       </c>
       <c r="F2011">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2011">
-        <v>0.02169709135861547</v>
+        <v>0.01989218411657986</v>
       </c>
       <c r="H2011">
-        <v>0.02172650795549707</v>
+        <v>0.01874676615750766</v>
       </c>
       <c r="I2011">
-        <v>0.2105834031183953</v>
+        <v>0.2145820409278016</v>
       </c>
       <c r="J2011">
-        <v>2.264585077959884</v>
+        <v>2.115536177600905</v>
       </c>
       <c r="K2011">
-        <v>4.6</v>
+        <v>4.26</v>
       </c>
       <c r="L2011">
-        <v>11.28</v>
+        <v>10.88</v>
       </c>
       <c r="M2011">
-        <v>4.56</v>
+        <v>4.04</v>
       </c>
       <c r="N2011">
-        <v>11.4</v>
+        <v>10.2</v>
       </c>
       <c r="O2011">
         <v>1</v>
@@ -102210,46 +102219,46 @@
     </row>
     <row r="2012" spans="1:16">
       <c r="A2012" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2012" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C2012">
-        <v>0.6946588507397173</v>
+        <v>1.855903415852207</v>
       </c>
       <c r="D2012" t="s">
-        <v>625</v>
+        <v>370</v>
       </c>
       <c r="E2012">
-        <v>1.298159269450091</v>
+        <v>1.653233842492343</v>
       </c>
       <c r="F2012">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2012">
-        <v>0.02098534114926028</v>
+        <v>0.01958409658414779</v>
       </c>
       <c r="H2012">
-        <v>0.02050184073054991</v>
+        <v>0.01874676615750766</v>
       </c>
       <c r="I2012">
-        <v>0.6035004187103734</v>
+        <v>0.2026695733598647</v>
       </c>
       <c r="J2012">
-        <v>2.264585077959884</v>
+        <v>2.115536177600905</v>
       </c>
       <c r="K2012">
-        <v>4.48</v>
+        <v>4.19</v>
       </c>
       <c r="L2012">
-        <v>10.84</v>
+        <v>10.72</v>
       </c>
       <c r="M2012">
-        <v>4.24</v>
+        <v>4.04</v>
       </c>
       <c r="N2012">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="O2012">
         <v>1</v>
@@ -102260,346 +102269,346 @@
     </row>
     <row r="2013" spans="1:16">
       <c r="A2013" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2013" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C2013">
-        <v>1.232867567890894</v>
+        <v>1.142132396478898</v>
       </c>
       <c r="D2013" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="E2013">
-        <v>1.105784583482873</v>
+        <v>1.350287766944298</v>
       </c>
       <c r="F2013">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2013">
-        <v>0.02052713243210911</v>
+        <v>0.0214178676035211</v>
       </c>
       <c r="H2013">
-        <v>0.01949421541651713</v>
+        <v>0.0214497122330557</v>
       </c>
       <c r="I2013">
-        <v>0.1270829844080215</v>
+        <v>0.2081553704654002</v>
       </c>
       <c r="J2013">
-        <v>2.264585077959884</v>
+        <v>2.203884261635022</v>
       </c>
       <c r="K2013">
-        <v>4.26</v>
+        <v>4.6</v>
       </c>
       <c r="L2013">
-        <v>10.88</v>
+        <v>11.28</v>
       </c>
       <c r="M2013">
-        <v>4.06</v>
+        <v>4.56</v>
       </c>
       <c r="N2013">
-        <v>10.3</v>
+        <v>11.4</v>
       </c>
       <c r="O2013">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2013" t="s">
-        <v>809</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2014" spans="1:16">
       <c r="A2014" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2014" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C2014">
-        <v>1.231388523348086</v>
+        <v>0.9665985078750996</v>
       </c>
       <c r="D2014" t="s">
-        <v>384</v>
+        <v>625</v>
       </c>
       <c r="E2014">
-        <v>1.105784583482873</v>
+        <v>1.555530730667506</v>
       </c>
       <c r="F2014">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2014">
-        <v>0.02020861147665192</v>
+        <v>0.0207134014921249</v>
       </c>
       <c r="H2014">
-        <v>0.01949421541651713</v>
+        <v>0.02024446926933249</v>
       </c>
       <c r="I2014">
-        <v>0.1256039398652131</v>
+        <v>0.5889322227924065</v>
       </c>
       <c r="J2014">
-        <v>2.264585077959884</v>
+        <v>2.203884261635022</v>
       </c>
       <c r="K2014">
-        <v>4.19</v>
+        <v>4.48</v>
       </c>
       <c r="L2014">
-        <v>10.72</v>
+        <v>10.84</v>
       </c>
       <c r="M2014">
-        <v>4.06</v>
+        <v>4.24</v>
       </c>
       <c r="N2014">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="O2014">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2014" t="s">
-        <v>809</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2015" spans="1:16">
       <c r="A2015" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2015" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C2015">
-        <v>0.5840985338074312</v>
+        <v>1.491453045434808</v>
       </c>
       <c r="D2015" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="E2015">
-        <v>0.7971063726438867</v>
+        <v>1.29630758299451</v>
       </c>
       <c r="F2015">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2015">
-        <v>0.02197590146619257</v>
+        <v>0.0202685469545652</v>
       </c>
       <c r="H2015">
-        <v>0.02200289362735612</v>
+        <v>0.01910369241700549</v>
       </c>
       <c r="I2015">
-        <v>0.2130078388364556</v>
+        <v>0.1951454624402977</v>
       </c>
       <c r="J2015">
-        <v>2.325195970911428</v>
+        <v>2.203884261635022</v>
       </c>
       <c r="K2015">
-        <v>4.6</v>
+        <v>4.26</v>
       </c>
       <c r="L2015">
-        <v>11.28</v>
+        <v>10.88</v>
       </c>
       <c r="M2015">
-        <v>4.56</v>
+        <v>4.04</v>
       </c>
       <c r="N2015">
-        <v>11.4</v>
+        <v>10.2</v>
       </c>
       <c r="O2015">
         <v>1</v>
       </c>
       <c r="P2015" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2016" spans="1:16">
       <c r="A2016" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2016" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C2016">
-        <v>0.4231220503168007</v>
+        <v>1.485724943749258</v>
       </c>
       <c r="D2016" t="s">
-        <v>625</v>
+        <v>370</v>
       </c>
       <c r="E2016">
-        <v>1.041169083335545</v>
+        <v>1.29630758299451</v>
       </c>
       <c r="F2016">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2016">
-        <v>0.0212568779496832</v>
+        <v>0.01995427505625074</v>
       </c>
       <c r="H2016">
-        <v>0.02075883091666446</v>
+        <v>0.01910369241700549</v>
       </c>
       <c r="I2016">
-        <v>0.618047033018744</v>
+        <v>0.1894173607547476</v>
       </c>
       <c r="J2016">
-        <v>2.325195970911428</v>
+        <v>2.203884261635022</v>
       </c>
       <c r="K2016">
-        <v>4.48</v>
+        <v>4.19</v>
       </c>
       <c r="L2016">
-        <v>10.84</v>
+        <v>10.72</v>
       </c>
       <c r="M2016">
-        <v>4.24</v>
+        <v>4.04</v>
       </c>
       <c r="N2016">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="O2016">
         <v>1</v>
       </c>
       <c r="P2016" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="2017" spans="1:16">
       <c r="A2017" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2017" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C2017">
-        <v>0.9746651639173169</v>
+        <v>0.8629086413845322</v>
       </c>
       <c r="D2017" t="s">
-        <v>384</v>
+        <v>360</v>
       </c>
       <c r="E2017">
-        <v>0.859704358099604</v>
+        <v>1.073492044502927</v>
       </c>
       <c r="F2017">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2017">
-        <v>0.02078533483608268</v>
+        <v>0.02169709135861547</v>
       </c>
       <c r="H2017">
-        <v>0.0197402956419004</v>
+        <v>0.02172650795549707</v>
       </c>
       <c r="I2017">
-        <v>0.114960805817713</v>
+        <v>0.2105834031183953</v>
       </c>
       <c r="J2017">
-        <v>2.325195970911428</v>
+        <v>2.264585077959884</v>
       </c>
       <c r="K2017">
-        <v>4.26</v>
+        <v>4.6</v>
       </c>
       <c r="L2017">
-        <v>10.88</v>
+        <v>11.28</v>
       </c>
       <c r="M2017">
-        <v>4.06</v>
+        <v>4.56</v>
       </c>
       <c r="N2017">
-        <v>10.3</v>
+        <v>11.4</v>
       </c>
       <c r="O2017">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2017" t="s">
-        <v>368</v>
+        <v>810</v>
       </c>
     </row>
     <row r="2018" spans="1:16">
       <c r="A2018" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2018" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C2018">
-        <v>0.9774288818811154</v>
+        <v>0.6946588507397173</v>
       </c>
       <c r="D2018" t="s">
-        <v>384</v>
+        <v>625</v>
       </c>
       <c r="E2018">
-        <v>0.859704358099604</v>
+        <v>1.298159269450091</v>
       </c>
       <c r="F2018">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2018">
-        <v>0.02046257111811889</v>
+        <v>0.02098534114926028</v>
       </c>
       <c r="H2018">
-        <v>0.0197402956419004</v>
+        <v>0.02050184073054991</v>
       </c>
       <c r="I2018">
-        <v>0.1177245237815114</v>
+        <v>0.6035004187103734</v>
       </c>
       <c r="J2018">
-        <v>2.325195970911428</v>
+        <v>2.264585077959884</v>
       </c>
       <c r="K2018">
-        <v>4.19</v>
+        <v>4.48</v>
       </c>
       <c r="L2018">
-        <v>10.72</v>
+        <v>10.84</v>
       </c>
       <c r="M2018">
-        <v>4.06</v>
+        <v>4.24</v>
       </c>
       <c r="N2018">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="O2018">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2018" t="s">
-        <v>368</v>
+        <v>810</v>
       </c>
     </row>
     <row r="2019" spans="1:16">
       <c r="A2019" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2019" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="C2019">
-        <v>0.2768744254458557</v>
+        <v>1.232867567890894</v>
       </c>
       <c r="D2019" t="s">
-        <v>620</v>
+        <v>370</v>
       </c>
       <c r="E2019">
-        <v>0.5047141018569619</v>
+        <v>1.051076285042067</v>
       </c>
       <c r="F2019">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2019">
-        <v>0.02228312557455414</v>
+        <v>0.02052713243210911</v>
       </c>
       <c r="H2019">
-        <v>0.02241528589814304</v>
+        <v>0.01934892371495793</v>
       </c>
       <c r="I2019">
-        <v>0.2278396764111061</v>
+        <v>0.1817912828488275</v>
       </c>
       <c r="J2019">
-        <v>2.391983820555249</v>
+        <v>2.264585077959884</v>
       </c>
       <c r="K2019">
-        <v>4.6</v>
+        <v>4.26</v>
       </c>
       <c r="L2019">
-        <v>11.28</v>
+        <v>10.88</v>
       </c>
       <c r="M2019">
-        <v>4.58</v>
+        <v>4.04</v>
       </c>
       <c r="N2019">
-        <v>11.46</v>
+        <v>10.2</v>
       </c>
       <c r="O2019">
         <v>1</v>
@@ -102610,46 +102619,46 @@
     </row>
     <row r="2020" spans="1:16">
       <c r="A2020" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2020" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="C2020">
-        <v>0.325114910829198</v>
+        <v>1.231388523348086</v>
       </c>
       <c r="D2020" t="s">
-        <v>625</v>
+        <v>370</v>
       </c>
       <c r="E2020">
-        <v>0.7579886008457439</v>
+        <v>1.051076285042067</v>
       </c>
       <c r="F2020">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2020">
-        <v>0.02247488508917081</v>
+        <v>0.02020861147665192</v>
       </c>
       <c r="H2020">
-        <v>0.02104201139915425</v>
+        <v>0.01934892371495793</v>
       </c>
       <c r="I2020">
-        <v>0.432873690016546</v>
+        <v>0.1803122383060192</v>
       </c>
       <c r="J2020">
-        <v>2.391983820555249</v>
+        <v>2.264585077959884</v>
       </c>
       <c r="K2020">
-        <v>4.63</v>
+        <v>4.19</v>
       </c>
       <c r="L2020">
-        <v>11.4</v>
+        <v>10.72</v>
       </c>
       <c r="M2020">
-        <v>4.24</v>
+        <v>4.04</v>
       </c>
       <c r="N2020">
-        <v>10.9</v>
+        <v>10.2</v>
       </c>
       <c r="O2020">
         <v>1</v>
@@ -102660,199 +102669,199 @@
     </row>
     <row r="2021" spans="1:16">
       <c r="A2021" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2021" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C2021">
-        <v>0.1239124839124841</v>
+        <v>0.5840985338074312</v>
       </c>
       <c r="D2021" t="s">
-        <v>625</v>
+        <v>360</v>
       </c>
       <c r="E2021">
-        <v>0.7579886008457439</v>
+        <v>0.7971063726438867</v>
       </c>
       <c r="F2021">
         <v>1</v>
       </c>
       <c r="G2021">
-        <v>0.02155608751608751</v>
+        <v>0.02197590146619257</v>
       </c>
       <c r="H2021">
-        <v>0.02104201139915425</v>
+        <v>0.02200289362735612</v>
       </c>
       <c r="I2021">
-        <v>0.6340761169332598</v>
+        <v>0.2130078388364556</v>
       </c>
       <c r="J2021">
-        <v>2.391983820555249</v>
+        <v>2.325195970911428</v>
       </c>
       <c r="K2021">
-        <v>4.48</v>
+        <v>4.6</v>
       </c>
       <c r="L2021">
-        <v>10.84</v>
+        <v>11.28</v>
       </c>
       <c r="M2021">
-        <v>4.24</v>
+        <v>4.56</v>
       </c>
       <c r="N2021">
-        <v>10.9</v>
+        <v>11.4</v>
       </c>
       <c r="O2021">
         <v>1</v>
       </c>
       <c r="P2021" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2022" spans="1:16">
       <c r="A2022" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2022" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C2022">
-        <v>0.6901489244346415</v>
+        <v>0.4231220503168007</v>
       </c>
       <c r="D2022" t="s">
-        <v>384</v>
+        <v>625</v>
       </c>
       <c r="E2022">
-        <v>0.5885456885456914</v>
+        <v>1.041169083335545</v>
       </c>
       <c r="F2022">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2022">
-        <v>0.02106985107556536</v>
+        <v>0.0212568779496832</v>
       </c>
       <c r="H2022">
-        <v>0.02001145431145431</v>
+        <v>0.02075883091666446</v>
       </c>
       <c r="I2022">
-        <v>0.10160323588895</v>
+        <v>0.618047033018744</v>
       </c>
       <c r="J2022">
-        <v>2.391983820555249</v>
+        <v>2.325195970911428</v>
       </c>
       <c r="K2022">
-        <v>4.26</v>
+        <v>4.48</v>
       </c>
       <c r="L2022">
-        <v>10.88</v>
+        <v>10.84</v>
       </c>
       <c r="M2022">
-        <v>4.06</v>
+        <v>4.24</v>
       </c>
       <c r="N2022">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="O2022">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2022" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2023" spans="1:16">
       <c r="A2023" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2023" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C2023">
-        <v>0.6975877918735076</v>
+        <v>0.9746651639173169</v>
       </c>
       <c r="D2023" t="s">
         <v>384</v>
       </c>
       <c r="E2023">
-        <v>0.5885456885456914</v>
+        <v>0.9244210430446582</v>
       </c>
       <c r="F2023">
         <v>-1</v>
       </c>
       <c r="G2023">
-        <v>0.0207424122081265</v>
+        <v>0.02078533483608268</v>
       </c>
       <c r="H2023">
-        <v>0.02001145431145431</v>
+        <v>0.02059557895695534</v>
       </c>
       <c r="I2023">
-        <v>0.1090421033278162</v>
+        <v>0.05024412087265873</v>
       </c>
       <c r="J2023">
-        <v>2.391983820555249</v>
+        <v>2.325195970911428</v>
       </c>
       <c r="K2023">
-        <v>4.19</v>
+        <v>4.26</v>
       </c>
       <c r="L2023">
-        <v>10.72</v>
+        <v>10.88</v>
       </c>
       <c r="M2023">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="N2023">
-        <v>10.3</v>
+        <v>10.76</v>
       </c>
       <c r="O2023">
         <v>0</v>
       </c>
       <c r="P2023" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2024" spans="1:16">
       <c r="A2024" s="1">
+        <v>3</v>
+      </c>
+      <c r="B2024" t="s">
+        <v>372</v>
+      </c>
+      <c r="C2024">
+        <v>0.9774288818811154</v>
+      </c>
+      <c r="D2024" t="s">
+        <v>384</v>
+      </c>
+      <c r="E2024">
+        <v>0.9244210430446582</v>
+      </c>
+      <c r="F2024">
+        <v>-1</v>
+      </c>
+      <c r="G2024">
+        <v>0.02046257111811889</v>
+      </c>
+      <c r="H2024">
+        <v>0.02059557895695534</v>
+      </c>
+      <c r="I2024">
+        <v>0.05300783883645721</v>
+      </c>
+      <c r="J2024">
+        <v>2.325195970911428</v>
+      </c>
+      <c r="K2024">
+        <v>4.19</v>
+      </c>
+      <c r="L2024">
+        <v>10.72</v>
+      </c>
+      <c r="M2024">
+        <v>4.23</v>
+      </c>
+      <c r="N2024">
+        <v>10.76</v>
+      </c>
+      <c r="O2024">
         <v>0</v>
-      </c>
-      <c r="B2024" t="s">
-        <v>378</v>
-      </c>
-      <c r="C2024">
-        <v>0.1945553716982218</v>
-      </c>
-      <c r="D2024" t="s">
-        <v>626</v>
-      </c>
-      <c r="E2024">
-        <v>0.434555371698222</v>
-      </c>
-      <c r="F2024">
-        <v>1</v>
-      </c>
-      <c r="G2024">
-        <v>0.02236544462830178</v>
-      </c>
-      <c r="H2024">
-        <v>0.02260544462830178</v>
-      </c>
-      <c r="I2024">
-        <v>0.2400000000000002</v>
-      </c>
-      <c r="J2024">
-        <v>2.409879267022126</v>
-      </c>
-      <c r="K2024">
-        <v>4.6</v>
-      </c>
-      <c r="L2024">
-        <v>11.28</v>
-      </c>
-      <c r="M2024">
-        <v>4.6</v>
-      </c>
-      <c r="N2024">
-        <v>11.52</v>
-      </c>
-      <c r="O2024">
-        <v>1</v>
       </c>
       <c r="P2024" t="s">
         <v>811</v>
@@ -102860,90 +102869,90 @@
     </row>
     <row r="2025" spans="1:16">
       <c r="A2025" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2025" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C2025">
-        <v>0.2422589936875585</v>
+        <v>0.2768744254458557</v>
       </c>
       <c r="D2025" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E2025">
-        <v>0.6821119078261866</v>
+        <v>0.5168744254458559</v>
       </c>
       <c r="F2025">
         <v>1</v>
       </c>
       <c r="G2025">
-        <v>0.02255774100631244</v>
+        <v>0.02228312557455414</v>
       </c>
       <c r="H2025">
-        <v>0.02111788809217382</v>
+        <v>0.02252312557455415</v>
       </c>
       <c r="I2025">
-        <v>0.439852914138628</v>
+        <v>0.2400000000000002</v>
       </c>
       <c r="J2025">
-        <v>2.409879267022126</v>
+        <v>2.391983820555249</v>
       </c>
       <c r="K2025">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="L2025">
-        <v>11.4</v>
+        <v>11.28</v>
       </c>
       <c r="M2025">
-        <v>4.24</v>
+        <v>4.6</v>
       </c>
       <c r="N2025">
-        <v>10.9</v>
+        <v>11.52</v>
       </c>
       <c r="O2025">
         <v>1</v>
       </c>
       <c r="P2025" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="2026" spans="1:16">
       <c r="A2026" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2026" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C2026">
-        <v>0.0437408837408757</v>
+        <v>0.325114910829198</v>
       </c>
       <c r="D2026" t="s">
         <v>625</v>
       </c>
       <c r="E2026">
-        <v>0.6821119078261866</v>
+        <v>0.7579886008457439</v>
       </c>
       <c r="F2026">
         <v>1</v>
       </c>
       <c r="G2026">
-        <v>0.02163625911625913</v>
+        <v>0.02247488508917081</v>
       </c>
       <c r="H2026">
-        <v>0.02111788809217382</v>
+        <v>0.02104201139915425</v>
       </c>
       <c r="I2026">
-        <v>0.6383710240853109</v>
+        <v>0.432873690016546</v>
       </c>
       <c r="J2026">
-        <v>2.409879267022126</v>
+        <v>2.391983820555249</v>
       </c>
       <c r="K2026">
-        <v>4.48</v>
+        <v>4.63</v>
       </c>
       <c r="L2026">
-        <v>10.84</v>
+        <v>11.4</v>
       </c>
       <c r="M2026">
         <v>4.24</v>
@@ -102955,195 +102964,195 @@
         <v>1</v>
       </c>
       <c r="P2026" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="2027" spans="1:16">
       <c r="A2027" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2027" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C2027">
-        <v>0.613914322485746</v>
+        <v>0.1239124839124841</v>
       </c>
       <c r="D2027" t="s">
-        <v>384</v>
+        <v>625</v>
       </c>
       <c r="E2027">
-        <v>0.5158901758901706</v>
+        <v>0.7579886008457439</v>
       </c>
       <c r="F2027">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2027">
-        <v>0.02114608567751426</v>
+        <v>0.02155608751608751</v>
       </c>
       <c r="H2027">
-        <v>0.02008410982410983</v>
+        <v>0.02104201139915425</v>
       </c>
       <c r="I2027">
-        <v>0.09802414659557535</v>
+        <v>0.6340761169332598</v>
       </c>
       <c r="J2027">
-        <v>2.409879267022126</v>
+        <v>2.391983820555249</v>
       </c>
       <c r="K2027">
-        <v>4.26</v>
+        <v>4.48</v>
       </c>
       <c r="L2027">
-        <v>10.88</v>
+        <v>10.84</v>
       </c>
       <c r="M2027">
-        <v>4.06</v>
+        <v>4.24</v>
       </c>
       <c r="N2027">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="O2027">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2027" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="2028" spans="1:16">
       <c r="A2028" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2028" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C2028">
-        <v>0.6226058711772922</v>
+        <v>0.6901489244346415</v>
       </c>
       <c r="D2028" t="s">
         <v>384</v>
       </c>
       <c r="E2028">
-        <v>0.5158901758901706</v>
+        <v>0.6419084390512957</v>
       </c>
       <c r="F2028">
         <v>-1</v>
       </c>
       <c r="G2028">
-        <v>0.02081739412882271</v>
+        <v>0.02106985107556536</v>
       </c>
       <c r="H2028">
-        <v>0.02008410982410983</v>
+        <v>0.02087809156094871</v>
       </c>
       <c r="I2028">
-        <v>0.1067156952871215</v>
+        <v>0.0482404853833458</v>
       </c>
       <c r="J2028">
-        <v>2.409879267022126</v>
+        <v>2.391983820555249</v>
       </c>
       <c r="K2028">
-        <v>4.19</v>
+        <v>4.26</v>
       </c>
       <c r="L2028">
-        <v>10.72</v>
+        <v>10.88</v>
       </c>
       <c r="M2028">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="N2028">
-        <v>10.3</v>
+        <v>10.76</v>
       </c>
       <c r="O2028">
         <v>0</v>
       </c>
       <c r="P2028" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="2029" spans="1:16">
       <c r="A2029" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2029" t="s">
+        <v>372</v>
+      </c>
+      <c r="C2029">
+        <v>0.6975877918735076</v>
+      </c>
+      <c r="D2029" t="s">
+        <v>384</v>
+      </c>
+      <c r="E2029">
+        <v>0.6419084390512957</v>
+      </c>
+      <c r="F2029">
+        <v>-1</v>
+      </c>
+      <c r="G2029">
+        <v>0.0207424122081265</v>
+      </c>
+      <c r="H2029">
+        <v>0.02087809156094871</v>
+      </c>
+      <c r="I2029">
+        <v>0.05567935282221192</v>
+      </c>
+      <c r="J2029">
+        <v>2.391983820555249</v>
+      </c>
+      <c r="K2029">
+        <v>4.19</v>
+      </c>
+      <c r="L2029">
+        <v>10.72</v>
+      </c>
+      <c r="M2029">
+        <v>4.23</v>
+      </c>
+      <c r="N2029">
+        <v>10.76</v>
+      </c>
+      <c r="O2029">
         <v>0</v>
       </c>
-      <c r="B2029" t="s">
-        <v>378</v>
-      </c>
-      <c r="C2029">
-        <v>-0.0197326876587649</v>
-      </c>
-      <c r="D2029" t="s">
-        <v>625</v>
-      </c>
-      <c r="E2029">
-        <v>0.484594218331921</v>
-      </c>
-      <c r="F2029">
-        <v>1</v>
-      </c>
-      <c r="G2029">
-        <v>0.02257973268765876</v>
-      </c>
-      <c r="H2029">
-        <v>0.02131540578166808</v>
-      </c>
-      <c r="I2029">
-        <v>0.5043269059906859</v>
-      </c>
-      <c r="J2029">
-        <v>2.456463627751905</v>
-      </c>
-      <c r="K2029">
-        <v>4.6</v>
-      </c>
-      <c r="L2029">
-        <v>11.28</v>
-      </c>
-      <c r="M2029">
-        <v>4.24</v>
-      </c>
-      <c r="N2029">
-        <v>10.9</v>
-      </c>
-      <c r="O2029">
-        <v>1</v>
-      </c>
       <c r="P2029" t="s">
-        <v>373</v>
+        <v>812</v>
       </c>
     </row>
     <row r="2030" spans="1:16">
       <c r="A2030" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2030" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C2030">
-        <v>0.02657340350867798</v>
+        <v>0.1945553716982218</v>
       </c>
       <c r="D2030" t="s">
         <v>625</v>
       </c>
       <c r="E2030">
-        <v>0.484594218331921</v>
+        <v>0.6821119078261866</v>
       </c>
       <c r="F2030">
         <v>1</v>
       </c>
       <c r="G2030">
-        <v>0.02277342659649132</v>
+        <v>0.02236544462830178</v>
       </c>
       <c r="H2030">
-        <v>0.02131540578166808</v>
+        <v>0.02111788809217382</v>
       </c>
       <c r="I2030">
-        <v>0.458020814823243</v>
+        <v>0.4875565361279648</v>
       </c>
       <c r="J2030">
-        <v>2.456463627751905</v>
+        <v>2.409879267022126</v>
       </c>
       <c r="K2030">
-        <v>4.63</v>
+        <v>4.6</v>
       </c>
       <c r="L2030">
-        <v>11.4</v>
+        <v>11.28</v>
       </c>
       <c r="M2030">
         <v>4.24</v>
@@ -103160,40 +103169,40 @@
     </row>
     <row r="2031" spans="1:16">
       <c r="A2031" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2031" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C2031">
-        <v>-0.1649570523285373</v>
+        <v>0.2422589936875585</v>
       </c>
       <c r="D2031" t="s">
         <v>625</v>
       </c>
       <c r="E2031">
-        <v>0.484594218331921</v>
+        <v>0.6821119078261866</v>
       </c>
       <c r="F2031">
         <v>1</v>
       </c>
       <c r="G2031">
-        <v>0.02184495705232854</v>
+        <v>0.02255774100631244</v>
       </c>
       <c r="H2031">
-        <v>0.02131540578166808</v>
+        <v>0.02111788809217382</v>
       </c>
       <c r="I2031">
-        <v>0.6495512706604583</v>
+        <v>0.439852914138628</v>
       </c>
       <c r="J2031">
-        <v>2.456463627751905</v>
+        <v>2.409879267022126</v>
       </c>
       <c r="K2031">
-        <v>4.48</v>
+        <v>4.63</v>
       </c>
       <c r="L2031">
-        <v>10.84</v>
+        <v>11.4</v>
       </c>
       <c r="M2031">
         <v>4.24</v>
@@ -103210,49 +103219,49 @@
     </row>
     <row r="2032" spans="1:16">
       <c r="A2032" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2032" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C2032">
-        <v>0.4154649457768844</v>
+        <v>0.0437408837408757</v>
       </c>
       <c r="D2032" t="s">
-        <v>384</v>
+        <v>625</v>
       </c>
       <c r="E2032">
-        <v>0.3267576713272664</v>
+        <v>0.6821119078261866</v>
       </c>
       <c r="F2032">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2032">
-        <v>0.02134453505422312</v>
+        <v>0.02163625911625913</v>
       </c>
       <c r="H2032">
-        <v>0.02027324232867274</v>
+        <v>0.02111788809217382</v>
       </c>
       <c r="I2032">
-        <v>0.08870727444961801</v>
+        <v>0.6383710240853109</v>
       </c>
       <c r="J2032">
-        <v>2.456463627751905</v>
+        <v>2.409879267022126</v>
       </c>
       <c r="K2032">
-        <v>4.26</v>
+        <v>4.48</v>
       </c>
       <c r="L2032">
-        <v>10.88</v>
+        <v>10.84</v>
       </c>
       <c r="M2032">
-        <v>4.06</v>
+        <v>4.24</v>
       </c>
       <c r="N2032">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="O2032">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2032" t="s">
         <v>373</v>
@@ -103260,46 +103269,46 @@
     </row>
     <row r="2033" spans="1:16">
       <c r="A2033" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2033" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C2033">
-        <v>0.4274173997195163</v>
+        <v>0.613914322485746</v>
       </c>
       <c r="D2033" t="s">
         <v>384</v>
       </c>
       <c r="E2033">
-        <v>0.3267576713272664</v>
+        <v>0.5662107004964057</v>
       </c>
       <c r="F2033">
         <v>-1</v>
       </c>
       <c r="G2033">
-        <v>0.02101258260028049</v>
+        <v>0.02114608567751426</v>
       </c>
       <c r="H2033">
-        <v>0.02027324232867274</v>
+        <v>0.0209537892995036</v>
       </c>
       <c r="I2033">
-        <v>0.1006597283922499</v>
+        <v>0.04770362198934031</v>
       </c>
       <c r="J2033">
-        <v>2.456463627751905</v>
+        <v>2.409879267022126</v>
       </c>
       <c r="K2033">
-        <v>4.19</v>
+        <v>4.26</v>
       </c>
       <c r="L2033">
-        <v>10.72</v>
+        <v>10.88</v>
       </c>
       <c r="M2033">
-        <v>4.06</v>
+        <v>4.23</v>
       </c>
       <c r="N2033">
-        <v>10.3</v>
+        <v>10.76</v>
       </c>
       <c r="O2033">
         <v>0</v>
@@ -103310,390 +103319,390 @@
     </row>
     <row r="2034" spans="1:16">
       <c r="A2034" s="1">
+        <v>4</v>
+      </c>
+      <c r="B2034" t="s">
+        <v>372</v>
+      </c>
+      <c r="C2034">
+        <v>0.6226058711772922</v>
+      </c>
+      <c r="D2034" t="s">
+        <v>384</v>
+      </c>
+      <c r="E2034">
+        <v>0.5662107004964057</v>
+      </c>
+      <c r="F2034">
+        <v>-1</v>
+      </c>
+      <c r="G2034">
+        <v>0.02081739412882271</v>
+      </c>
+      <c r="H2034">
+        <v>0.0209537892995036</v>
+      </c>
+      <c r="I2034">
+        <v>0.05639517068088651</v>
+      </c>
+      <c r="J2034">
+        <v>2.409879267022126</v>
+      </c>
+      <c r="K2034">
+        <v>4.19</v>
+      </c>
+      <c r="L2034">
+        <v>10.72</v>
+      </c>
+      <c r="M2034">
+        <v>4.23</v>
+      </c>
+      <c r="N2034">
+        <v>10.76</v>
+      </c>
+      <c r="O2034">
         <v>0</v>
       </c>
-      <c r="B2034" t="s">
-        <v>378</v>
-      </c>
-      <c r="C2034">
-        <v>0.1487066885472412</v>
-      </c>
-      <c r="D2034" t="s">
-        <v>374</v>
-      </c>
-      <c r="E2034">
-        <v>-0.0009117468061656808</v>
-      </c>
-      <c r="F2034">
-        <v>1</v>
-      </c>
-      <c r="G2034">
-        <v>0.02241129331145276</v>
-      </c>
-      <c r="H2034">
-        <v>0.02168091174680617</v>
-      </c>
-      <c r="I2034">
-        <v>-0.1496184353534069</v>
-      </c>
-      <c r="J2034">
-        <v>2.419846372054947</v>
-      </c>
-      <c r="K2034">
-        <v>4.6</v>
-      </c>
-      <c r="L2034">
-        <v>11.28</v>
-      </c>
-      <c r="M2034">
-        <v>4.48</v>
-      </c>
-      <c r="N2034">
-        <v>10.84</v>
-      </c>
-      <c r="O2034">
-        <v>1</v>
-      </c>
       <c r="P2034" t="s">
-        <v>624</v>
+        <v>373</v>
       </c>
     </row>
     <row r="2035" spans="1:16">
       <c r="A2035" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2035" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C2035">
-        <v>0.2519128336650454</v>
+        <v>-0.0197326876587649</v>
       </c>
       <c r="D2035" t="s">
-        <v>374</v>
+        <v>625</v>
       </c>
       <c r="E2035">
-        <v>-0.0009117468061656808</v>
+        <v>0.484594218331921</v>
       </c>
       <c r="F2035">
         <v>1</v>
       </c>
       <c r="G2035">
-        <v>0.02270808716633495</v>
+        <v>0.02257973268765876</v>
       </c>
       <c r="H2035">
-        <v>0.02168091174680617</v>
+        <v>0.02131540578166808</v>
       </c>
       <c r="I2035">
-        <v>-0.252824580471211</v>
+        <v>0.5043269059906859</v>
       </c>
       <c r="J2035">
-        <v>2.419846372054947</v>
+        <v>2.456463627751905</v>
       </c>
       <c r="K2035">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="L2035">
-        <v>11.48</v>
+        <v>11.28</v>
       </c>
       <c r="M2035">
-        <v>4.48</v>
+        <v>4.24</v>
       </c>
       <c r="N2035">
-        <v>10.84</v>
+        <v>10.9</v>
       </c>
       <c r="O2035">
         <v>1</v>
       </c>
       <c r="P2035" t="s">
-        <v>624</v>
+        <v>813</v>
       </c>
     </row>
     <row r="2036" spans="1:16">
       <c r="A2036" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2036" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C2036">
-        <v>0.5714544550459255</v>
+        <v>0.02657340350867798</v>
       </c>
       <c r="D2036" t="s">
-        <v>384</v>
+        <v>625</v>
       </c>
       <c r="E2036">
-        <v>0.4754237294569155</v>
+        <v>0.484594218331921</v>
       </c>
       <c r="F2036">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2036">
-        <v>0.02118854554495407</v>
+        <v>0.02277342659649132</v>
       </c>
       <c r="H2036">
-        <v>0.02012457627054309</v>
+        <v>0.02131540578166808</v>
       </c>
       <c r="I2036">
-        <v>0.09603072558901005</v>
+        <v>0.458020814823243</v>
       </c>
       <c r="J2036">
-        <v>2.419846372054947</v>
+        <v>2.456463627751905</v>
       </c>
       <c r="K2036">
-        <v>4.26</v>
+        <v>4.63</v>
       </c>
       <c r="L2036">
-        <v>10.88</v>
+        <v>11.4</v>
       </c>
       <c r="M2036">
-        <v>4.06</v>
+        <v>4.24</v>
       </c>
       <c r="N2036">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="O2036">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2036" t="s">
-        <v>624</v>
+        <v>813</v>
       </c>
     </row>
     <row r="2037" spans="1:16">
       <c r="A2037" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2037" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C2037">
-        <v>0.5808437010897691</v>
+        <v>-0.1649570523285373</v>
       </c>
       <c r="D2037" t="s">
-        <v>384</v>
+        <v>625</v>
       </c>
       <c r="E2037">
-        <v>0.4754237294569155</v>
+        <v>0.484594218331921</v>
       </c>
       <c r="F2037">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2037">
-        <v>0.02085915629891023</v>
+        <v>0.02184495705232854</v>
       </c>
       <c r="H2037">
-        <v>0.02012457627054309</v>
+        <v>0.02131540578166808</v>
       </c>
       <c r="I2037">
-        <v>0.1054199716328537</v>
+        <v>0.6495512706604583</v>
       </c>
       <c r="J2037">
-        <v>2.419846372054947</v>
+        <v>2.456463627751905</v>
       </c>
       <c r="K2037">
-        <v>4.19</v>
+        <v>4.48</v>
       </c>
       <c r="L2037">
-        <v>10.72</v>
+        <v>10.84</v>
       </c>
       <c r="M2037">
-        <v>4.06</v>
+        <v>4.24</v>
       </c>
       <c r="N2037">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="O2037">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2037" t="s">
-        <v>624</v>
+        <v>813</v>
       </c>
     </row>
     <row r="2038" spans="1:16">
       <c r="A2038" s="1">
+        <v>3</v>
+      </c>
+      <c r="B2038" t="s">
+        <v>371</v>
+      </c>
+      <c r="C2038">
+        <v>0.4154649457768844</v>
+      </c>
+      <c r="D2038" t="s">
+        <v>384</v>
+      </c>
+      <c r="E2038">
+        <v>0.369158854609438</v>
+      </c>
+      <c r="F2038">
+        <v>-1</v>
+      </c>
+      <c r="G2038">
+        <v>0.02134453505422312</v>
+      </c>
+      <c r="H2038">
+        <v>0.02115084114539056</v>
+      </c>
+      <c r="I2038">
+        <v>0.04630609116744644</v>
+      </c>
+      <c r="J2038">
+        <v>2.456463627751905</v>
+      </c>
+      <c r="K2038">
+        <v>4.26</v>
+      </c>
+      <c r="L2038">
+        <v>10.88</v>
+      </c>
+      <c r="M2038">
+        <v>4.23</v>
+      </c>
+      <c r="N2038">
+        <v>10.76</v>
+      </c>
+      <c r="O2038">
         <v>0</v>
       </c>
-      <c r="B2038" t="s">
-        <v>379</v>
-      </c>
-      <c r="C2038">
-        <v>0.8075673659959435</v>
-      </c>
-      <c r="D2038" t="s">
-        <v>374</v>
-      </c>
-      <c r="E2038">
-        <v>0.5907347299485561</v>
-      </c>
-      <c r="F2038">
-        <v>1</v>
-      </c>
-      <c r="G2038">
-        <v>0.02199243263400406</v>
-      </c>
-      <c r="H2038">
-        <v>0.02108926527005144</v>
-      </c>
-      <c r="I2038">
-        <v>-0.2168326360473873</v>
-      </c>
-      <c r="J2038">
-        <v>2.287782426350768</v>
-      </c>
-      <c r="K2038">
-        <v>4.63</v>
-      </c>
-      <c r="L2038">
-        <v>11.4</v>
-      </c>
-      <c r="M2038">
-        <v>4.48</v>
-      </c>
-      <c r="N2038">
-        <v>10.84</v>
-      </c>
-      <c r="O2038">
-        <v>1</v>
-      </c>
       <c r="P2038" t="s">
-        <v>378</v>
+        <v>813</v>
       </c>
     </row>
     <row r="2039" spans="1:16">
       <c r="A2039" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2039" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C2039">
-        <v>1.134046863745727</v>
+        <v>0.4274173997195163</v>
       </c>
       <c r="D2039" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="E2039">
-        <v>0.9770694578537871</v>
+        <v>0.369158854609438</v>
       </c>
       <c r="F2039">
         <v>-1</v>
       </c>
       <c r="G2039">
-        <v>0.02062595313625427</v>
+        <v>0.02101258260028049</v>
       </c>
       <c r="H2039">
-        <v>0.02010293054214621</v>
+        <v>0.02115084114539056</v>
       </c>
       <c r="I2039">
-        <v>0.15697740589194</v>
+        <v>0.05825854511007833</v>
       </c>
       <c r="J2039">
-        <v>2.287782426350768</v>
+        <v>2.456463627751905</v>
       </c>
       <c r="K2039">
-        <v>4.26</v>
+        <v>4.19</v>
       </c>
       <c r="L2039">
-        <v>10.88</v>
+        <v>10.72</v>
       </c>
       <c r="M2039">
-        <v>4.18</v>
+        <v>4.23</v>
       </c>
       <c r="N2039">
-        <v>10.54</v>
+        <v>10.76</v>
       </c>
       <c r="O2039">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2039" t="s">
-        <v>378</v>
+        <v>813</v>
       </c>
     </row>
     <row r="2040" spans="1:16">
       <c r="A2040" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2040" t="s">
         <v>377</v>
       </c>
       <c r="C2040">
-        <v>1.13419163359028</v>
+        <v>0.1487066885472412</v>
       </c>
       <c r="D2040" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="E2040">
-        <v>0.9770694578537871</v>
+        <v>-0.0009117468061656808</v>
       </c>
       <c r="F2040">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2040">
-        <v>0.02030580836640972</v>
+        <v>0.02241129331145276</v>
       </c>
       <c r="H2040">
-        <v>0.02010293054214621</v>
+        <v>0.02168091174680617</v>
       </c>
       <c r="I2040">
-        <v>0.1571221757364931</v>
+        <v>-0.1496184353534069</v>
       </c>
       <c r="J2040">
-        <v>2.287782426350768</v>
+        <v>2.419846372054947</v>
       </c>
       <c r="K2040">
-        <v>4.19</v>
+        <v>4.6</v>
       </c>
       <c r="L2040">
-        <v>10.72</v>
+        <v>11.28</v>
       </c>
       <c r="M2040">
-        <v>4.18</v>
+        <v>4.48</v>
       </c>
       <c r="N2040">
-        <v>10.54</v>
+        <v>10.84</v>
       </c>
       <c r="O2040">
         <v>1</v>
       </c>
       <c r="P2040" t="s">
-        <v>378</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2041" spans="1:16">
       <c r="A2041" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2041" t="s">
         <v>379</v>
       </c>
       <c r="C2041">
-        <v>1.035536769851644</v>
+        <v>0.2519128336650454</v>
       </c>
       <c r="D2041" t="s">
         <v>374</v>
       </c>
       <c r="E2041">
-        <v>0.811318515968761</v>
+        <v>-0.0009117468061656808</v>
       </c>
       <c r="F2041">
         <v>1</v>
       </c>
       <c r="G2041">
-        <v>0.02176446323014836</v>
+        <v>0.02270808716633495</v>
       </c>
       <c r="H2041">
-        <v>0.02086868148403124</v>
+        <v>0.02168091174680617</v>
       </c>
       <c r="I2041">
-        <v>-0.2242182538828832</v>
+        <v>-0.252824580471211</v>
       </c>
       <c r="J2041">
-        <v>2.238544974114116</v>
+        <v>2.419846372054947</v>
       </c>
       <c r="K2041">
-        <v>4.63</v>
+        <v>4.64</v>
       </c>
       <c r="L2041">
-        <v>11.4</v>
+        <v>11.48</v>
       </c>
       <c r="M2041">
         <v>4.48</v>
@@ -103705,39 +103714,39 @@
         <v>1</v>
       </c>
       <c r="P2041" t="s">
-        <v>812</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2042" spans="1:16">
       <c r="A2042" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2042" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="C2042">
-        <v>1.343798410273868</v>
+        <v>0.5714544550459255</v>
       </c>
       <c r="D2042" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="E2042">
-        <v>1.182882008202997</v>
+        <v>0.5240498462075713</v>
       </c>
       <c r="F2042">
         <v>-1</v>
       </c>
       <c r="G2042">
-        <v>0.02041620158972613</v>
+        <v>0.02118854554495407</v>
       </c>
       <c r="H2042">
-        <v>0.019897117991797</v>
+        <v>0.02099595015379243</v>
       </c>
       <c r="I2042">
-        <v>0.1609164020708711</v>
+        <v>0.04740460883835418</v>
       </c>
       <c r="J2042">
-        <v>2.238544974114116</v>
+        <v>2.419846372054947</v>
       </c>
       <c r="K2042">
         <v>4.26</v>
@@ -103746,66 +103755,66 @@
         <v>10.88</v>
       </c>
       <c r="M2042">
-        <v>4.18</v>
+        <v>4.23</v>
       </c>
       <c r="N2042">
-        <v>10.54</v>
+        <v>10.76</v>
       </c>
       <c r="O2042">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2042" t="s">
-        <v>812</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2043" spans="1:16">
       <c r="A2043" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2043" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="C2043">
-        <v>1.360496558461854</v>
+        <v>0.5808437010897691</v>
       </c>
       <c r="D2043" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="E2043">
-        <v>1.182882008202997</v>
+        <v>0.5240498462075713</v>
       </c>
       <c r="F2043">
         <v>-1</v>
       </c>
       <c r="G2043">
-        <v>0.02011950344153815</v>
+        <v>0.02085915629891023</v>
       </c>
       <c r="H2043">
-        <v>0.019897117991797</v>
+        <v>0.02099595015379243</v>
       </c>
       <c r="I2043">
-        <v>0.1776145502588573</v>
+        <v>0.05679385488219779</v>
       </c>
       <c r="J2043">
-        <v>2.238544974114116</v>
+        <v>2.419846372054947</v>
       </c>
       <c r="K2043">
         <v>4.19</v>
       </c>
       <c r="L2043">
-        <v>10.74</v>
+        <v>10.72</v>
       </c>
       <c r="M2043">
-        <v>4.18</v>
+        <v>4.23</v>
       </c>
       <c r="N2043">
-        <v>10.54</v>
+        <v>10.76</v>
       </c>
       <c r="O2043">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2043" t="s">
-        <v>812</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2044" spans="1:16">
@@ -103813,31 +103822,31 @@
         <v>0</v>
       </c>
       <c r="B2044" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C2044">
-        <v>1.549549298192899</v>
+        <v>0.8075673659959435</v>
       </c>
       <c r="D2044" t="s">
         <v>374</v>
       </c>
       <c r="E2044">
-        <v>1.308678370605655</v>
+        <v>0.5907347299485561</v>
       </c>
       <c r="F2044">
         <v>1</v>
       </c>
       <c r="G2044">
-        <v>0.0212504507018071</v>
+        <v>0.02199243263400406</v>
       </c>
       <c r="H2044">
-        <v>0.02037132162939434</v>
+        <v>0.02108926527005144</v>
       </c>
       <c r="I2044">
-        <v>-0.2408709275872436</v>
+        <v>-0.2168326360473873</v>
       </c>
       <c r="J2044">
-        <v>2.127527149418381</v>
+        <v>2.287782426350768</v>
       </c>
       <c r="K2044">
         <v>4.63</v>
@@ -103855,7 +103864,7 @@
         <v>1</v>
       </c>
       <c r="P2044" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2045" spans="1:16">
@@ -103863,37 +103872,37 @@
         <v>1</v>
       </c>
       <c r="B2045" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="C2045">
-        <v>1.825661243936985</v>
+        <v>1.134046863745727</v>
       </c>
       <c r="D2045" t="s">
         <v>366</v>
       </c>
       <c r="E2045">
-        <v>1.64693651543117</v>
+        <v>0.9770694578537871</v>
       </c>
       <c r="F2045">
         <v>-1</v>
       </c>
       <c r="G2045">
-        <v>0.01965433875606301</v>
+        <v>0.02062595313625427</v>
       </c>
       <c r="H2045">
-        <v>0.01943306348456883</v>
+        <v>0.02010293054214621</v>
       </c>
       <c r="I2045">
-        <v>0.1787247285058147</v>
+        <v>0.15697740589194</v>
       </c>
       <c r="J2045">
-        <v>2.127527149418381</v>
+        <v>2.287782426350768</v>
       </c>
       <c r="K2045">
-        <v>4.19</v>
+        <v>4.26</v>
       </c>
       <c r="L2045">
-        <v>10.74</v>
+        <v>10.88</v>
       </c>
       <c r="M2045">
         <v>4.18</v>
@@ -103905,307 +103914,307 @@
         <v>1</v>
       </c>
       <c r="P2045" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2046" spans="1:16">
       <c r="A2046" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2046" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="C2046">
-        <v>2.004813860193888</v>
+        <v>1.13419163359028</v>
       </c>
       <c r="D2046" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="E2046">
-        <v>1.749193540749159</v>
+        <v>0.9770694578537871</v>
       </c>
       <c r="F2046">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2046">
-        <v>0.02079518613980611</v>
+        <v>0.02030580836640972</v>
       </c>
       <c r="H2046">
-        <v>0.01993080645925084</v>
+        <v>0.02010293054214621</v>
       </c>
       <c r="I2046">
-        <v>-0.2556203194447288</v>
+        <v>0.1571221757364931</v>
       </c>
       <c r="J2046">
-        <v>2.029197870368491</v>
+        <v>2.287782426350768</v>
       </c>
       <c r="K2046">
-        <v>4.63</v>
+        <v>4.19</v>
       </c>
       <c r="L2046">
-        <v>11.4</v>
+        <v>10.72</v>
       </c>
       <c r="M2046">
-        <v>4.48</v>
+        <v>4.18</v>
       </c>
       <c r="N2046">
-        <v>10.84</v>
+        <v>10.54</v>
       </c>
       <c r="O2046">
         <v>1</v>
       </c>
       <c r="P2046" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2047" spans="1:16">
       <c r="A2047" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2047" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C2047">
-        <v>2.275033114822859</v>
+        <v>1.093151320110504</v>
       </c>
       <c r="D2047" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="E2047">
-        <v>2.057952901859707</v>
+        <v>0.811318515968761</v>
       </c>
       <c r="F2047">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2047">
-        <v>0.01964496688517714</v>
+        <v>0.0218668486798895</v>
       </c>
       <c r="H2047">
-        <v>0.01902204709814029</v>
+        <v>0.02086868148403124</v>
       </c>
       <c r="I2047">
-        <v>0.2170802129631522</v>
+        <v>-0.2818328041417431</v>
       </c>
       <c r="J2047">
-        <v>2.029197870368491</v>
+        <v>2.238544974114116</v>
       </c>
       <c r="K2047">
-        <v>4.28</v>
+        <v>4.64</v>
       </c>
       <c r="L2047">
-        <v>10.96</v>
+        <v>11.48</v>
       </c>
       <c r="M2047">
-        <v>4.18</v>
+        <v>4.48</v>
       </c>
       <c r="N2047">
-        <v>10.54</v>
+        <v>10.84</v>
       </c>
       <c r="O2047">
         <v>1</v>
       </c>
       <c r="P2047" t="s">
-        <v>360</v>
+        <v>814</v>
       </c>
     </row>
     <row r="2048" spans="1:16">
       <c r="A2048" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2048" t="s">
         <v>371</v>
       </c>
       <c r="C2048">
-        <v>2.002040603711295</v>
+        <v>1.343798410273868</v>
       </c>
       <c r="D2048" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="E2048">
-        <v>2.061456646303927</v>
+        <v>1.182882008202997</v>
       </c>
       <c r="F2048">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2048">
-        <v>0.01839795939628871</v>
+        <v>0.02041620158972613</v>
       </c>
       <c r="H2048">
-        <v>0.01853854335369607</v>
+        <v>0.019897117991797</v>
       </c>
       <c r="I2048">
-        <v>0.05941604259263222</v>
+        <v>0.1609164020708711</v>
       </c>
       <c r="J2048">
-        <v>2.029197870368491</v>
+        <v>2.238544974114116</v>
       </c>
       <c r="K2048">
-        <v>4.04</v>
+        <v>4.26</v>
       </c>
       <c r="L2048">
-        <v>10.2</v>
+        <v>10.88</v>
       </c>
       <c r="M2048">
-        <v>4.06</v>
+        <v>4.18</v>
       </c>
       <c r="N2048">
-        <v>10.3</v>
+        <v>10.54</v>
       </c>
       <c r="O2048">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2048" t="s">
-        <v>360</v>
+        <v>814</v>
       </c>
     </row>
     <row r="2049" spans="1:16">
       <c r="A2049" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2049" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C2049">
-        <v>2.520452503404956</v>
+        <v>1.360496558461854</v>
       </c>
       <c r="D2049" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="E2049">
-        <v>2.276032497848609</v>
+        <v>1.182882008202997</v>
       </c>
       <c r="F2049">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2049">
-        <v>0.01983954749659505</v>
+        <v>0.02011950344153815</v>
       </c>
       <c r="H2049">
-        <v>0.01940396750215139</v>
+        <v>0.019897117991797</v>
       </c>
       <c r="I2049">
-        <v>-0.2444200055563464</v>
+        <v>0.1776145502588573</v>
       </c>
       <c r="J2049">
-        <v>1.911599888873078</v>
+        <v>2.238544974114116</v>
       </c>
       <c r="K2049">
-        <v>4.53</v>
+        <v>4.19</v>
       </c>
       <c r="L2049">
-        <v>11.18</v>
+        <v>10.74</v>
       </c>
       <c r="M2049">
-        <v>4.48</v>
+        <v>4.18</v>
       </c>
       <c r="N2049">
-        <v>10.84</v>
+        <v>10.54</v>
       </c>
       <c r="O2049">
         <v>1</v>
       </c>
       <c r="P2049" t="s">
-        <v>620</v>
+        <v>814</v>
       </c>
     </row>
     <row r="2050" spans="1:16">
       <c r="A2050" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2050" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C2050">
-        <v>2.778352475623226</v>
+        <v>1.549549298192899</v>
       </c>
       <c r="D2050" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="E2050">
-        <v>2.549512464510533</v>
+        <v>1.308678370605655</v>
       </c>
       <c r="F2050">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2050">
-        <v>0.01914164752437678</v>
+        <v>0.0212504507018071</v>
       </c>
       <c r="H2050">
-        <v>0.01853048753548946</v>
+        <v>0.02037132162939434</v>
       </c>
       <c r="I2050">
-        <v>0.2288400111126929</v>
+        <v>-0.2408709275872436</v>
       </c>
       <c r="J2050">
-        <v>1.911599888873078</v>
+        <v>2.127527149418381</v>
       </c>
       <c r="K2050">
-        <v>4.28</v>
+        <v>4.63</v>
       </c>
       <c r="L2050">
-        <v>10.96</v>
+        <v>11.4</v>
       </c>
       <c r="M2050">
-        <v>4.18</v>
+        <v>4.48</v>
       </c>
       <c r="N2050">
-        <v>10.54</v>
+        <v>10.84</v>
       </c>
       <c r="O2050">
         <v>1</v>
       </c>
       <c r="P2050" t="s">
-        <v>620</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2051" spans="1:16">
       <c r="A2051" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2051" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="C2051">
-        <v>2.477136448952764</v>
+        <v>1.825661243936985</v>
       </c>
       <c r="D2051" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="E2051">
-        <v>2.538904451175305</v>
+        <v>1.64693651543117</v>
       </c>
       <c r="F2051">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2051">
-        <v>0.01792286355104724</v>
+        <v>0.01965433875606301</v>
       </c>
       <c r="H2051">
-        <v>0.0180610955488247</v>
+        <v>0.01943306348456883</v>
       </c>
       <c r="I2051">
-        <v>0.06176800222254109</v>
+        <v>0.1787247285058147</v>
       </c>
       <c r="J2051">
-        <v>1.911599888873078</v>
+        <v>2.127527149418381</v>
       </c>
       <c r="K2051">
-        <v>4.04</v>
+        <v>4.19</v>
       </c>
       <c r="L2051">
-        <v>10.2</v>
+        <v>10.74</v>
       </c>
       <c r="M2051">
-        <v>4.06</v>
+        <v>4.18</v>
       </c>
       <c r="N2051">
-        <v>10.3</v>
+        <v>10.54</v>
       </c>
       <c r="O2051">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2051" t="s">
-        <v>620</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2052" spans="1:16">
@@ -104213,49 +104222,49 @@
         <v>0</v>
       </c>
       <c r="B2052" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C2052">
-        <v>3.323473137107757</v>
+        <v>2.004813860193888</v>
       </c>
       <c r="D2052" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="E2052">
-        <v>3.081896661941688</v>
+        <v>1.749193540749159</v>
       </c>
       <c r="F2052">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2052">
-        <v>0.01859652686289225</v>
+        <v>0.02079518613980611</v>
       </c>
       <c r="H2052">
-        <v>0.01799810333805831</v>
+        <v>0.01993080645925084</v>
       </c>
       <c r="I2052">
-        <v>0.2415764751660694</v>
+        <v>-0.2556203194447288</v>
       </c>
       <c r="J2052">
-        <v>1.784235248339309</v>
+        <v>2.029197870368491</v>
       </c>
       <c r="K2052">
-        <v>4.28</v>
+        <v>4.63</v>
       </c>
       <c r="L2052">
-        <v>10.96</v>
+        <v>11.4</v>
       </c>
       <c r="M2052">
-        <v>4.18</v>
+        <v>4.48</v>
       </c>
       <c r="N2052">
-        <v>10.54</v>
+        <v>10.84</v>
       </c>
       <c r="O2052">
         <v>1</v>
       </c>
       <c r="P2052" t="s">
-        <v>813</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2053" spans="1:16">
@@ -104263,28 +104272,49 @@
         <v>1</v>
       </c>
       <c r="B2053" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="C2053">
-        <v>2.991689596709191</v>
+        <v>2.275033114822859</v>
+      </c>
+      <c r="D2053" t="s">
+        <v>366</v>
+      </c>
+      <c r="E2053">
+        <v>2.057952901859707</v>
       </c>
       <c r="F2053">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2053">
-        <v>0.01740831040329081</v>
+        <v>0.01964496688517714</v>
+      </c>
+      <c r="H2053">
+        <v>0.01902204709814029</v>
+      </c>
+      <c r="I2053">
+        <v>0.2170802129631522</v>
       </c>
       <c r="J2053">
-        <v>1.784235248339309</v>
+        <v>2.029197870368491</v>
       </c>
       <c r="K2053">
-        <v>4.04</v>
+        <v>4.28</v>
       </c>
       <c r="L2053">
-        <v>10.2</v>
+        <v>10.96</v>
+      </c>
+      <c r="M2053">
+        <v>4.18</v>
+      </c>
+      <c r="N2053">
+        <v>10.54</v>
+      </c>
+      <c r="O2053">
+        <v>1</v>
       </c>
       <c r="P2053" t="s">
-        <v>813</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2054" spans="1:16">
@@ -104292,28 +104322,49 @@
         <v>2</v>
       </c>
       <c r="B2054" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="C2054">
-        <v>3.056004891742407</v>
+        <v>2.002040603711295</v>
+      </c>
+      <c r="D2054" t="s">
+        <v>376</v>
+      </c>
+      <c r="E2054">
+        <v>2.157952901859709</v>
       </c>
       <c r="F2054">
         <v>1</v>
       </c>
       <c r="G2054">
-        <v>0.01754399510825759</v>
+        <v>0.01839795939628871</v>
+      </c>
+      <c r="H2054">
+        <v>0.01912204709814029</v>
+      </c>
+      <c r="I2054">
+        <v>0.1559122981484133</v>
       </c>
       <c r="J2054">
-        <v>1.784235248339309</v>
+        <v>2.029197870368491</v>
       </c>
       <c r="K2054">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="L2054">
-        <v>10.3</v>
+        <v>10.2</v>
+      </c>
+      <c r="M2054">
+        <v>4.18</v>
+      </c>
+      <c r="N2054">
+        <v>10.64</v>
+      </c>
+      <c r="O2054">
+        <v>1</v>
       </c>
       <c r="P2054" t="s">
-        <v>813</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2055" spans="1:16">
@@ -104324,46 +104375,46 @@
         <v>382</v>
       </c>
       <c r="C2055">
-        <v>3.270408885976819</v>
+        <v>2.520452503404956</v>
       </c>
       <c r="D2055" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="E2055">
-        <v>3.030072229762407</v>
+        <v>2.276032497848609</v>
       </c>
       <c r="F2055">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2055">
-        <v>0.01864959111402318</v>
+        <v>0.01983954749659505</v>
       </c>
       <c r="H2055">
-        <v>0.01804992777023759</v>
+        <v>0.01940396750215139</v>
       </c>
       <c r="I2055">
-        <v>0.2403366562144118</v>
+        <v>-0.2444200055563464</v>
       </c>
       <c r="J2055">
-        <v>1.796633437855883</v>
+        <v>1.911599888873078</v>
       </c>
       <c r="K2055">
-        <v>4.28</v>
+        <v>4.53</v>
       </c>
       <c r="L2055">
-        <v>10.96</v>
+        <v>11.18</v>
       </c>
       <c r="M2055">
-        <v>4.18</v>
+        <v>4.48</v>
       </c>
       <c r="N2055">
-        <v>10.54</v>
+        <v>10.84</v>
       </c>
       <c r="O2055">
         <v>1</v>
       </c>
       <c r="P2055" t="s">
-        <v>379</v>
+        <v>620</v>
       </c>
     </row>
     <row r="2056" spans="1:16">
@@ -104371,257 +104422,728 @@
         <v>1</v>
       </c>
       <c r="B2056" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="C2056">
-        <v>2.94160091106223</v>
+        <v>2.778352475623226</v>
       </c>
       <c r="D2056" t="s">
-        <v>384</v>
+        <v>366</v>
       </c>
       <c r="E2056">
-        <v>3.005668242305115</v>
+        <v>2.549512464510533</v>
       </c>
       <c r="F2056">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2056">
-        <v>0.01745839908893777</v>
+        <v>0.01914164752437678</v>
       </c>
       <c r="H2056">
-        <v>0.01759433175769489</v>
+        <v>0.01853048753548946</v>
       </c>
       <c r="I2056">
-        <v>0.06406733124288433</v>
+        <v>0.2288400111126929</v>
       </c>
       <c r="J2056">
-        <v>1.796633437855883</v>
+        <v>1.911599888873078</v>
       </c>
       <c r="K2056">
-        <v>4.04</v>
+        <v>4.28</v>
       </c>
       <c r="L2056">
-        <v>10.2</v>
+        <v>10.96</v>
       </c>
       <c r="M2056">
-        <v>4.06</v>
+        <v>4.18</v>
       </c>
       <c r="N2056">
-        <v>10.3</v>
+        <v>10.54</v>
       </c>
       <c r="O2056">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2056" t="s">
-        <v>379</v>
+        <v>620</v>
       </c>
     </row>
     <row r="2057" spans="1:16">
       <c r="A2057" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2057" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="C2057">
-        <v>3.362882443212659</v>
+        <v>2.477136448952764</v>
       </c>
       <c r="D2057" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="E2057">
-        <v>3.120385189866568</v>
+        <v>2.649512464510535</v>
       </c>
       <c r="F2057">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2057">
-        <v>0.01855711755678734</v>
+        <v>0.01792286355104724</v>
       </c>
       <c r="H2057">
-        <v>0.01795961481013343</v>
+        <v>0.01863048753548947</v>
       </c>
       <c r="I2057">
-        <v>0.242497253346091</v>
+        <v>0.1723760155577709</v>
       </c>
       <c r="J2057">
-        <v>1.775027466539098</v>
+        <v>1.911599888873078</v>
       </c>
       <c r="K2057">
-        <v>4.28</v>
+        <v>4.04</v>
       </c>
       <c r="L2057">
-        <v>10.96</v>
+        <v>10.2</v>
       </c>
       <c r="M2057">
         <v>4.18</v>
       </c>
       <c r="N2057">
-        <v>10.54</v>
+        <v>10.64</v>
       </c>
       <c r="O2057">
         <v>1</v>
       </c>
       <c r="P2057" t="s">
-        <v>383</v>
+        <v>620</v>
       </c>
     </row>
     <row r="2058" spans="1:16">
       <c r="A2058" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2058" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="C2058">
-        <v>3.028889035182042</v>
+        <v>3.323473137107757</v>
+      </c>
+      <c r="D2058" t="s">
+        <v>366</v>
+      </c>
+      <c r="E2058">
+        <v>3.081896661941688</v>
       </c>
       <c r="F2058">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G2058">
-        <v>0.01737111096481796</v>
+        <v>0.01859652686289225</v>
+      </c>
+      <c r="H2058">
+        <v>0.01799810333805831</v>
+      </c>
+      <c r="I2058">
+        <v>0.2415764751660694</v>
       </c>
       <c r="J2058">
-        <v>1.775027466539098</v>
+        <v>1.784235248339309</v>
       </c>
       <c r="K2058">
-        <v>4.04</v>
+        <v>4.28</v>
       </c>
       <c r="L2058">
-        <v>10.2</v>
+        <v>10.96</v>
+      </c>
+      <c r="M2058">
+        <v>4.18</v>
+      </c>
+      <c r="N2058">
+        <v>10.54</v>
+      </c>
+      <c r="O2058">
+        <v>1</v>
       </c>
       <c r="P2058" t="s">
-        <v>383</v>
+        <v>815</v>
       </c>
     </row>
     <row r="2059" spans="1:16">
       <c r="A2059" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2059" t="s">
-        <v>384</v>
+        <v>370</v>
       </c>
       <c r="C2059">
-        <v>3.093388485851262</v>
+        <v>2.991689596709191</v>
+      </c>
+      <c r="D2059" t="s">
+        <v>376</v>
+      </c>
+      <c r="E2059">
+        <v>3.181896661941689</v>
       </c>
       <c r="F2059">
         <v>1</v>
       </c>
       <c r="G2059">
-        <v>0.01750661151414874</v>
+        <v>0.01740831040329081</v>
+      </c>
+      <c r="H2059">
+        <v>0.01809810333805831</v>
+      </c>
+      <c r="I2059">
+        <v>0.1902070652324985</v>
       </c>
       <c r="J2059">
-        <v>1.775027466539098</v>
+        <v>1.784235248339309</v>
       </c>
       <c r="K2059">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="L2059">
-        <v>10.3</v>
+        <v>10.2</v>
+      </c>
+      <c r="M2059">
+        <v>4.18</v>
+      </c>
+      <c r="N2059">
+        <v>10.64</v>
+      </c>
+      <c r="O2059">
+        <v>1</v>
       </c>
       <c r="P2059" t="s">
-        <v>383</v>
+        <v>815</v>
       </c>
     </row>
     <row r="2060" spans="1:16">
       <c r="A2060" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2060" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C2060">
-        <v>3.227800769260446</v>
+        <v>3.056004891742407</v>
       </c>
       <c r="D2060" t="s">
-        <v>627</v>
+        <v>376</v>
       </c>
       <c r="E2060">
-        <v>3.095537225047926</v>
+        <v>3.181896661941689</v>
       </c>
       <c r="F2060">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G2060">
-        <v>0.01869219923073956</v>
+        <v>0.01754399510825759</v>
       </c>
       <c r="H2060">
-        <v>0.01870446277495207</v>
+        <v>0.01809810333805831</v>
       </c>
       <c r="I2060">
-        <v>0.1322635442125195</v>
+        <v>0.1258917701992823</v>
       </c>
       <c r="J2060">
-        <v>1.80658860531298</v>
+        <v>1.784235248339309</v>
       </c>
       <c r="K2060">
-        <v>4.28</v>
+        <v>4.06</v>
       </c>
       <c r="L2060">
-        <v>10.96</v>
+        <v>10.3</v>
       </c>
       <c r="M2060">
-        <v>4.32</v>
+        <v>4.18</v>
       </c>
       <c r="N2060">
-        <v>10.9</v>
+        <v>10.64</v>
       </c>
       <c r="O2060">
         <v>1</v>
       </c>
       <c r="P2060" t="s">
-        <v>625</v>
+        <v>815</v>
       </c>
     </row>
     <row r="2061" spans="1:16">
       <c r="A2061" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2061" t="s">
+        <v>381</v>
+      </c>
+      <c r="C2061">
+        <v>3.270408885976819</v>
+      </c>
+      <c r="D2061" t="s">
         <v>366</v>
       </c>
-      <c r="C2061">
+      <c r="E2061">
+        <v>3.030072229762407</v>
+      </c>
+      <c r="F2061">
+        <v>-1</v>
+      </c>
+      <c r="G2061">
+        <v>0.01864959111402318</v>
+      </c>
+      <c r="H2061">
+        <v>0.01804992777023759</v>
+      </c>
+      <c r="I2061">
+        <v>0.2403366562144118</v>
+      </c>
+      <c r="J2061">
+        <v>1.796633437855883</v>
+      </c>
+      <c r="K2061">
+        <v>4.28</v>
+      </c>
+      <c r="L2061">
+        <v>10.96</v>
+      </c>
+      <c r="M2061">
+        <v>4.18</v>
+      </c>
+      <c r="N2061">
+        <v>10.54</v>
+      </c>
+      <c r="O2061">
+        <v>1</v>
+      </c>
+      <c r="P2061" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:16">
+      <c r="A2062" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2062" t="s">
+        <v>370</v>
+      </c>
+      <c r="C2062">
+        <v>2.94160091106223</v>
+      </c>
+      <c r="D2062" t="s">
+        <v>376</v>
+      </c>
+      <c r="E2062">
+        <v>3.130072229762408</v>
+      </c>
+      <c r="F2062">
+        <v>1</v>
+      </c>
+      <c r="G2062">
+        <v>0.01745839908893777</v>
+      </c>
+      <c r="H2062">
+        <v>0.01814992777023759</v>
+      </c>
+      <c r="I2062">
+        <v>0.1884713187001781</v>
+      </c>
+      <c r="J2062">
+        <v>1.796633437855883</v>
+      </c>
+      <c r="K2062">
+        <v>4.04</v>
+      </c>
+      <c r="L2062">
+        <v>10.2</v>
+      </c>
+      <c r="M2062">
+        <v>4.18</v>
+      </c>
+      <c r="N2062">
+        <v>10.64</v>
+      </c>
+      <c r="O2062">
+        <v>1</v>
+      </c>
+      <c r="P2062" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:16">
+      <c r="A2063" s="1">
+        <v>2</v>
+      </c>
+      <c r="B2063" t="s">
+        <v>383</v>
+      </c>
+      <c r="C2063">
+        <v>3.005668242305115</v>
+      </c>
+      <c r="D2063" t="s">
+        <v>376</v>
+      </c>
+      <c r="E2063">
+        <v>3.130072229762408</v>
+      </c>
+      <c r="F2063">
+        <v>1</v>
+      </c>
+      <c r="G2063">
+        <v>0.01759433175769489</v>
+      </c>
+      <c r="H2063">
+        <v>0.01814992777023759</v>
+      </c>
+      <c r="I2063">
+        <v>0.1244039874572938</v>
+      </c>
+      <c r="J2063">
+        <v>1.796633437855883</v>
+      </c>
+      <c r="K2063">
+        <v>4.06</v>
+      </c>
+      <c r="L2063">
+        <v>10.3</v>
+      </c>
+      <c r="M2063">
+        <v>4.18</v>
+      </c>
+      <c r="N2063">
+        <v>10.64</v>
+      </c>
+      <c r="O2063">
+        <v>1</v>
+      </c>
+      <c r="P2063" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:16">
+      <c r="A2064" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2064" t="s">
+        <v>381</v>
+      </c>
+      <c r="C2064">
+        <v>3.362882443212659</v>
+      </c>
+      <c r="D2064" t="s">
+        <v>366</v>
+      </c>
+      <c r="E2064">
+        <v>3.120385189866568</v>
+      </c>
+      <c r="F2064">
+        <v>-1</v>
+      </c>
+      <c r="G2064">
+        <v>0.01855711755678734</v>
+      </c>
+      <c r="H2064">
+        <v>0.01795961481013343</v>
+      </c>
+      <c r="I2064">
+        <v>0.242497253346091</v>
+      </c>
+      <c r="J2064">
+        <v>1.775027466539098</v>
+      </c>
+      <c r="K2064">
+        <v>4.28</v>
+      </c>
+      <c r="L2064">
+        <v>10.96</v>
+      </c>
+      <c r="M2064">
+        <v>4.18</v>
+      </c>
+      <c r="N2064">
+        <v>10.54</v>
+      </c>
+      <c r="O2064">
+        <v>1</v>
+      </c>
+      <c r="P2064" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="2065" spans="1:16">
+      <c r="A2065" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2065" t="s">
+        <v>370</v>
+      </c>
+      <c r="C2065">
+        <v>3.028889035182042</v>
+      </c>
+      <c r="D2065" t="s">
+        <v>376</v>
+      </c>
+      <c r="E2065">
+        <v>3.22038518986657</v>
+      </c>
+      <c r="F2065">
+        <v>1</v>
+      </c>
+      <c r="G2065">
+        <v>0.01737111096481796</v>
+      </c>
+      <c r="H2065">
+        <v>0.01805961481013343</v>
+      </c>
+      <c r="I2065">
+        <v>0.1914961546845282</v>
+      </c>
+      <c r="J2065">
+        <v>1.775027466539098</v>
+      </c>
+      <c r="K2065">
+        <v>4.04</v>
+      </c>
+      <c r="L2065">
+        <v>10.2</v>
+      </c>
+      <c r="M2065">
+        <v>4.18</v>
+      </c>
+      <c r="N2065">
+        <v>10.64</v>
+      </c>
+      <c r="O2065">
+        <v>1</v>
+      </c>
+      <c r="P2065" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:16">
+      <c r="A2066" s="1">
+        <v>2</v>
+      </c>
+      <c r="B2066" t="s">
+        <v>383</v>
+      </c>
+      <c r="C2066">
+        <v>3.093388485851262</v>
+      </c>
+      <c r="D2066" t="s">
+        <v>376</v>
+      </c>
+      <c r="E2066">
+        <v>3.22038518986657</v>
+      </c>
+      <c r="F2066">
+        <v>1</v>
+      </c>
+      <c r="G2066">
+        <v>0.01750661151414874</v>
+      </c>
+      <c r="H2066">
+        <v>0.01805961481013343</v>
+      </c>
+      <c r="I2066">
+        <v>0.1269967040153075</v>
+      </c>
+      <c r="J2066">
+        <v>1.775027466539098</v>
+      </c>
+      <c r="K2066">
+        <v>4.06</v>
+      </c>
+      <c r="L2066">
+        <v>10.3</v>
+      </c>
+      <c r="M2066">
+        <v>4.18</v>
+      </c>
+      <c r="N2066">
+        <v>10.64</v>
+      </c>
+      <c r="O2066">
+        <v>1</v>
+      </c>
+      <c r="P2066" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:16">
+      <c r="A2067" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2067" t="s">
+        <v>381</v>
+      </c>
+      <c r="C2067">
+        <v>3.227800769260446</v>
+      </c>
+      <c r="D2067" t="s">
+        <v>627</v>
+      </c>
+      <c r="E2067">
+        <v>3.095537225047926</v>
+      </c>
+      <c r="F2067">
+        <v>-1</v>
+      </c>
+      <c r="G2067">
+        <v>0.01869219923073956</v>
+      </c>
+      <c r="H2067">
+        <v>0.01870446277495207</v>
+      </c>
+      <c r="I2067">
+        <v>0.1322635442125195</v>
+      </c>
+      <c r="J2067">
+        <v>1.80658860531298</v>
+      </c>
+      <c r="K2067">
+        <v>4.28</v>
+      </c>
+      <c r="L2067">
+        <v>10.96</v>
+      </c>
+      <c r="M2067">
+        <v>4.32</v>
+      </c>
+      <c r="N2067">
+        <v>10.9</v>
+      </c>
+      <c r="O2067">
+        <v>1</v>
+      </c>
+      <c r="P2067" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:16">
+      <c r="A2068" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2068" t="s">
+        <v>366</v>
+      </c>
+      <c r="C2068">
         <v>2.988459629791743</v>
       </c>
-      <c r="D2061" t="s">
+      <c r="D2068" t="s">
         <v>384</v>
       </c>
-      <c r="E2061">
-        <v>2.965250262429302</v>
-      </c>
-      <c r="F2061">
-        <v>1</v>
-      </c>
-      <c r="G2061">
+      <c r="E2068">
+        <v>3.118130199526093</v>
+      </c>
+      <c r="F2068">
+        <v>1</v>
+      </c>
+      <c r="G2068">
         <v>0.01809154037020826</v>
       </c>
-      <c r="H2061">
-        <v>0.0176347497375707</v>
-      </c>
-      <c r="I2061">
-        <v>-0.0232093673624405</v>
-      </c>
-      <c r="J2061">
+      <c r="H2068">
+        <v>0.01840186980047391</v>
+      </c>
+      <c r="I2068">
+        <v>0.1296705697343503</v>
+      </c>
+      <c r="J2068">
         <v>1.80658860531298</v>
       </c>
-      <c r="K2061">
+      <c r="K2068">
         <v>4.18</v>
       </c>
-      <c r="L2061">
+      <c r="L2068">
         <v>10.54</v>
       </c>
-      <c r="M2061">
+      <c r="M2068">
+        <v>4.23</v>
+      </c>
+      <c r="N2068">
+        <v>10.76</v>
+      </c>
+      <c r="O2068">
+        <v>1</v>
+      </c>
+      <c r="P2068" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:16">
+      <c r="A2069" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2069" t="s">
+        <v>383</v>
+      </c>
+      <c r="C2069">
+        <v>4.202117994847591</v>
+      </c>
+      <c r="D2069" t="s">
+        <v>376</v>
+      </c>
+      <c r="E2069">
+        <v>4.361885029178062</v>
+      </c>
+      <c r="F2069">
+        <v>1</v>
+      </c>
+      <c r="G2069">
+        <v>0.01639788200515241</v>
+      </c>
+      <c r="H2069">
+        <v>0.01691811497082194</v>
+      </c>
+      <c r="I2069">
+        <v>0.1597670343304705</v>
+      </c>
+      <c r="J2069">
+        <v>1.501941380579411</v>
+      </c>
+      <c r="K2069">
         <v>4.06</v>
       </c>
-      <c r="N2061">
+      <c r="L2069">
         <v>10.3</v>
       </c>
-      <c r="O2061">
-        <v>0</v>
-      </c>
-      <c r="P2061" t="s">
-        <v>625</v>
+      <c r="M2069">
+        <v>4.18</v>
+      </c>
+      <c r="N2069">
+        <v>10.64</v>
+      </c>
+      <c r="O2069">
+        <v>1</v>
+      </c>
+      <c r="P2069" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:16">
+      <c r="A2070" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2070" t="s">
+        <v>384</v>
+      </c>
+      <c r="C2070">
+        <v>4.40678796014909</v>
+      </c>
+      <c r="F2070">
+        <v>-1</v>
+      </c>
+      <c r="G2070">
+        <v>0.01711321203985091</v>
+      </c>
+      <c r="J2070">
+        <v>1.501941380579411</v>
+      </c>
+      <c r="K2070">
+        <v>4.23</v>
+      </c>
+      <c r="L2070">
+        <v>10.76</v>
+      </c>
+      <c r="P2070" t="s">
+        <v>816</v>
       </c>
     </row>
   </sheetData>
